--- a/исправления внести/слова3.xlsx
+++ b/исправления внести/слова3.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0313F8A7-80D2-4661-BE62-A8C2E53C186A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830D2B2A-E9E2-4FE0-98E1-31AFDCDB4708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="1" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
   </bookViews>
   <sheets>
-    <sheet name="одичночные" sheetId="1" r:id="rId1"/>
-    <sheet name="cоставные" sheetId="2" r:id="rId2"/>
-    <sheet name="автору отправить" sheetId="3" r:id="rId3"/>
+    <sheet name="cоставные" sheetId="2" r:id="rId1"/>
+    <sheet name="автору отправить" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,32 +37,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="855">
-  <si>
-    <t>исходные</t>
-  </si>
-  <si>
-    <t>перевод</t>
-  </si>
-  <si>
-    <t>энергоинформационный</t>
-  </si>
-  <si>
-    <t>фаллос</t>
-  </si>
-  <si>
-    <t>энвальтирование</t>
-  </si>
-  <si>
-    <t>эгрэгор</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="784">
   <si>
     <t>биологический структурализм</t>
   </si>
   <si>
-    <t>эксирополяция</t>
-  </si>
-  <si>
     <t>прямых излучения</t>
   </si>
   <si>
@@ -76,30 +54,12 @@
     <t>кто в этом случае</t>
   </si>
   <si>
-    <t>микролептонных</t>
-  </si>
-  <si>
-    <t>тахионных</t>
-  </si>
-  <si>
-    <t>спиновую</t>
-  </si>
-  <si>
-    <t>спиновое</t>
-  </si>
-  <si>
     <t>скрученой звездоведения</t>
   </si>
   <si>
     <t>скрученного звездоведения</t>
   </si>
   <si>
-    <t>животно</t>
-  </si>
-  <si>
-    <t>животное</t>
-  </si>
-  <si>
     <t>по крайней мере глуп</t>
   </si>
   <si>
@@ -118,165 +78,12 @@
     <t>возможны два исхода ее возврата</t>
   </si>
   <si>
-    <t>командировку</t>
-  </si>
-  <si>
-    <t xml:space="preserve">аквариумист </t>
-  </si>
-  <si>
-    <t>станции</t>
-  </si>
-  <si>
     <t>физическими рассчётами</t>
   </si>
   <si>
-    <t xml:space="preserve">Морфогенным </t>
-  </si>
-  <si>
-    <t xml:space="preserve">кодировку </t>
-  </si>
-  <si>
-    <t xml:space="preserve">спинирующего </t>
-  </si>
-  <si>
-    <t>тримеров, тетрамеров, пентамеров и гексамеров</t>
-  </si>
-  <si>
-    <t>органов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">энергетической </t>
-  </si>
-  <si>
-    <t xml:space="preserve">жестикулирующий </t>
-  </si>
-  <si>
-    <t>биоэнергетик</t>
-  </si>
-  <si>
-    <t>кампании</t>
-  </si>
-  <si>
-    <t xml:space="preserve">антиматерии </t>
-  </si>
-  <si>
-    <t xml:space="preserve">антимиры </t>
-  </si>
-  <si>
-    <t>антицивилизациями</t>
-  </si>
-  <si>
-    <t xml:space="preserve">космологический </t>
-  </si>
-  <si>
-    <t>робот</t>
-  </si>
-  <si>
-    <t xml:space="preserve">иммунную </t>
-  </si>
-  <si>
-    <t xml:space="preserve">голографическую </t>
-  </si>
-  <si>
-    <t xml:space="preserve">лазерных </t>
-  </si>
-  <si>
-    <t xml:space="preserve">фантомного </t>
-  </si>
-  <si>
-    <t xml:space="preserve">эниокорректору </t>
-  </si>
-  <si>
-    <t xml:space="preserve">метакодом </t>
-  </si>
-  <si>
-    <t xml:space="preserve">инвалидов </t>
-  </si>
-  <si>
-    <t xml:space="preserve">биополевой </t>
-  </si>
-  <si>
-    <t xml:space="preserve">кодированная </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Биоэнергетические </t>
-  </si>
-  <si>
-    <t xml:space="preserve">молекулой </t>
-  </si>
-  <si>
-    <t>нуклиды</t>
-  </si>
-  <si>
-    <t>радикалы</t>
-  </si>
-  <si>
-    <t xml:space="preserve">онкологией </t>
-  </si>
-  <si>
-    <t xml:space="preserve">неперсонификации </t>
-  </si>
-  <si>
-    <t xml:space="preserve">нуклон </t>
-  </si>
-  <si>
-    <t>синапсов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">биолокационными </t>
-  </si>
-  <si>
-    <t xml:space="preserve">абстрактный </t>
-  </si>
-  <si>
-    <t>энергетики</t>
-  </si>
-  <si>
-    <t>аура</t>
-  </si>
-  <si>
-    <t xml:space="preserve">модулятора </t>
-  </si>
-  <si>
     <t>контактантов</t>
   </si>
   <si>
-    <t xml:space="preserve">экологическая </t>
-  </si>
-  <si>
-    <t>медикаментов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">неоткорректированных </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ультрафиолетового </t>
-  </si>
-  <si>
-    <t xml:space="preserve">инфракрасного </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Хромосомы </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ультразвука </t>
-  </si>
-  <si>
-    <t>антиреинкарнационном</t>
-  </si>
-  <si>
-    <t>автокатастрофе</t>
-  </si>
-  <si>
-    <t xml:space="preserve">натальную </t>
-  </si>
-  <si>
-    <t xml:space="preserve">мембраны </t>
-  </si>
-  <si>
-    <t xml:space="preserve">романа </t>
-  </si>
-  <si>
     <t>тем самым занижает свой возможности разума</t>
   </si>
   <si>
@@ -1345,9 +1152,6 @@
     <t>оставляют ваше местоположение</t>
   </si>
   <si>
-    <t>энвольтировать</t>
-  </si>
-  <si>
     <t>молекул нашего живой особи</t>
   </si>
   <si>
@@ -1414,9 +1218,6 @@
     <t>еще одна важная особенность</t>
   </si>
   <si>
-    <t>панспермии</t>
-  </si>
-  <si>
     <t>не проводить изменение лунной витки</t>
   </si>
   <si>
@@ -1436,12 +1237,6 @@
   </si>
   <si>
     <t>в итоге всей этого случая</t>
-  </si>
-  <si>
-    <t>сериалу</t>
-  </si>
-  <si>
-    <t>дегустацию</t>
   </si>
   <si>
     <t>в итоге всего этого случая</t>
@@ -1841,12 +1636,6 @@
     </r>
   </si>
   <si>
-    <t>прейскурант:</t>
-  </si>
-  <si>
-    <t>телебоевиков</t>
-  </si>
-  <si>
     <t>устраивали еще одно проверка</t>
   </si>
   <si>
@@ -2613,9 +2402,6 @@
   </si>
   <si>
     <t>Мыслеобраза при проведении общего изменения</t>
-  </si>
-  <si>
-    <t> клевретов,</t>
   </si>
   <si>
     <t>выплеснула в космос всю накопленную заряд</t>
@@ -2628,29 +2414,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2750,26 +2520,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -3103,3444 +2869,3076 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7256F3A-5CBA-4182-B90F-37645EE12738}">
-  <dimension ref="A2:B70"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="1" max="1" width="35.7265625" customWidth="1"/>
-    <col min="2" max="2" width="54.81640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:2">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" s="12" t="s">
-        <v>852</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157B4C6A-53EA-4FB9-AB5B-06694B8739E0}">
   <dimension ref="A2:B431"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="72" style="7" customWidth="1"/>
-    <col min="2" max="2" width="67.26953125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="72" style="5" customWidth="1"/>
+    <col min="2" max="2" width="67.26953125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="5" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="7" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="10" t="s">
+    <row r="8" spans="1:2">
+      <c r="A8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="10" t="s">
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="6" t="s">
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="8" t="s">
+      <c r="B10" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="5" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="7" t="s">
+      <c r="B19" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B44" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="7" t="s">
+    <row r="45" spans="1:2">
+      <c r="A45" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B45" s="5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="7" t="s">
+    <row r="46" spans="1:2">
+      <c r="A46" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B46" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="7" t="s">
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B47" s="5" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="7" t="s">
+    <row r="48" spans="1:2">
+      <c r="A48" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B48" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="7" t="s">
+    <row r="49" spans="1:2">
+      <c r="A49" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B49" s="5" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="7" t="s">
+    <row r="50" spans="1:2">
+      <c r="A50" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B50" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="7" t="s">
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B51" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="7" t="s">
+    <row r="52" spans="1:2">
+      <c r="A52" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B52" s="5" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="7" t="s">
+    <row r="53" spans="1:2">
+      <c r="A53" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B53" s="5" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="7" t="s">
+    <row r="54" spans="1:2">
+      <c r="A54" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B54" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="7" t="s">
+    <row r="55" spans="1:2">
+      <c r="A55" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B55" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="7" t="s">
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B56" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="7" t="s">
+    <row r="57" spans="1:2">
+      <c r="A57" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B57" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="7" t="s">
+    <row r="58" spans="1:2">
+      <c r="A58" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B58" s="5" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="7" t="s">
+    <row r="59" spans="1:2">
+      <c r="A59" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B59" s="5" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="7" t="s">
+    <row r="60" spans="1:2">
+      <c r="A60" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B60" s="5" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="7" t="s">
+    <row r="61" spans="1:2">
+      <c r="A61" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B61" s="5" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="7" t="s">
+    <row r="62" spans="1:2">
+      <c r="A62" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B62" s="5" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="7" t="s">
+    <row r="63" spans="1:2">
+      <c r="A63" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B63" s="5" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="7" t="s">
+    <row r="64" spans="1:2">
+      <c r="A64" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B64" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="7" t="s">
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B65" s="5" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="7" t="s">
+    <row r="66" spans="1:2">
+      <c r="A66" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B66" s="5" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="7" t="s">
+    <row r="67" spans="1:2">
+      <c r="A67" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B67" s="5" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="7" t="s">
+    <row r="68" spans="1:2">
+      <c r="A68" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B68" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="7" t="s">
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B69" s="5" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="7" t="s">
+    <row r="70" spans="1:2">
+      <c r="A70" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B70" s="5" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="7" t="s">
+    <row r="71" spans="1:2">
+      <c r="A71" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B71" s="5" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="7" t="s">
+    <row r="72" spans="1:2">
+      <c r="A72" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B72" s="5" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="7" t="s">
+    <row r="73" spans="1:2">
+      <c r="A73" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="B73" s="5" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="7" t="s">
+    <row r="74" spans="1:2">
+      <c r="A74" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B74" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="7" t="s">
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B75" s="5" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="7" t="s">
+    <row r="76" spans="1:2">
+      <c r="A76" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B76" s="5" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="7" t="s">
+    <row r="77" spans="1:2">
+      <c r="A77" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B77" s="5" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="7" t="s">
+    <row r="78" spans="1:2">
+      <c r="A78" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B78" s="5" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="7" t="s">
+    <row r="79" spans="1:2">
+      <c r="A79" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B79" s="5" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="7" t="s">
+    <row r="80" spans="1:2">
+      <c r="A80" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B80" s="5" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="7" t="s">
+    <row r="81" spans="1:2">
+      <c r="A81" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B81" s="5" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="7" t="s">
+    <row r="82" spans="1:2">
+      <c r="A82" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B82" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="B50" s="7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="7" t="s">
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B83" s="5" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="7" t="s">
+    <row r="84" spans="1:2">
+      <c r="A84" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B84" s="5" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="7" t="s">
+    <row r="85" spans="1:2">
+      <c r="A85" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B85" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B53" s="7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="7" t="s">
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B86" s="5" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
-      <c r="A55" s="7" t="s">
+    <row r="87" spans="1:2">
+      <c r="A87" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B87" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="B55" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" s="7" t="s">
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B88" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="B56" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" s="7" t="s">
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B89" s="5" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
-      <c r="A58" s="7" t="s">
+    <row r="90" spans="1:2">
+      <c r="A90" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B90" s="5" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
-      <c r="A59" s="7" t="s">
+    <row r="91" spans="1:2">
+      <c r="A91" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B91" s="5" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
-      <c r="A60" s="7" t="s">
+    <row r="92" spans="1:2">
+      <c r="A92" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B92" s="5" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
-      <c r="A61" s="7" t="s">
+    <row r="93" spans="1:2">
+      <c r="A93" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="B61" s="7" t="s">
+      <c r="B93" s="5" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
-      <c r="A62" s="7" t="s">
+    <row r="94" spans="1:2">
+      <c r="A94" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="B62" s="7" t="s">
+      <c r="B94" s="5" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
-      <c r="A63" s="7" t="s">
+    <row r="95" spans="1:2">
+      <c r="A95" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="B63" s="7" t="s">
+      <c r="B95" s="5" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
-      <c r="A64" s="7" t="s">
+    <row r="96" spans="1:2">
+      <c r="A96" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B96" s="5" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
-      <c r="A65" s="7" t="s">
+    <row r="97" spans="1:2">
+      <c r="A97" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="B65" s="7" t="s">
+      <c r="B97" s="5" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
-      <c r="A66" s="7" t="s">
+    <row r="98" spans="1:2">
+      <c r="A98" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B66" s="7" t="s">
+      <c r="B98" s="5" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
-      <c r="A67" s="7" t="s">
+    <row r="99" spans="1:2">
+      <c r="A99" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="B67" s="7" t="s">
+      <c r="B99" s="5" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
-      <c r="A68" s="7" t="s">
+    <row r="100" spans="1:2">
+      <c r="A100" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B100" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="B68" s="7" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69" s="7" t="s">
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B69" s="7" t="s">
+      <c r="B101" s="5" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
-      <c r="A70" s="7" t="s">
+    <row r="102" spans="1:2">
+      <c r="A102" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B70" s="7" t="s">
+      <c r="B102" s="5" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
-      <c r="A71" s="7" t="s">
+    <row r="103" spans="1:2">
+      <c r="A103" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B71" s="7" t="s">
+      <c r="B103" s="5" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
-      <c r="A72" s="7" t="s">
+    <row r="104" spans="1:2">
+      <c r="A104" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B72" s="7" t="s">
+      <c r="B104" s="5" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
-      <c r="A73" s="7" t="s">
+    <row r="105" spans="1:2">
+      <c r="A105" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="B73" s="7" t="s">
+      <c r="B105" s="5" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
-      <c r="A74" s="7" t="s">
+    <row r="106" spans="1:2">
+      <c r="A106" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B106" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="B74" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
-      <c r="A75" s="7" t="s">
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="B75" s="7" t="s">
+      <c r="B107" s="5" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
-      <c r="A76" s="7" t="s">
+    <row r="108" spans="1:2">
+      <c r="A108" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="B108" s="5" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
-      <c r="A77" s="7" t="s">
+    <row r="109" spans="1:2">
+      <c r="A109" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B77" s="7" t="s">
+      <c r="B109" s="5" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
-      <c r="A78" s="7" t="s">
+    <row r="110" spans="1:2">
+      <c r="A110" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="B78" s="7" t="s">
+      <c r="B110" s="5" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
-      <c r="A79" s="7" t="s">
+    <row r="111" spans="1:2">
+      <c r="A111" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="B79" s="7" t="s">
+      <c r="B111" s="5" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
-      <c r="A80" s="7" t="s">
+    <row r="112" spans="1:2">
+      <c r="A112" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="B80" s="7" t="s">
+      <c r="B112" s="5" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
-      <c r="A81" s="7" t="s">
+    <row r="113" spans="1:2">
+      <c r="A113" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B81" s="7" t="s">
+      <c r="B113" s="5" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
-      <c r="A82" s="7" t="s">
+    <row r="114" spans="1:2">
+      <c r="A114" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="B82" s="7" t="s">
+      <c r="B114" s="5" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
-      <c r="A83" s="7" t="s">
+    <row r="115" spans="1:2">
+      <c r="A115" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="B83" s="7" t="s">
+      <c r="B115" s="5" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
-      <c r="A84" s="7" t="s">
+    <row r="116" spans="1:2">
+      <c r="A116" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="B84" s="7" t="s">
+      <c r="B116" s="5" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
-      <c r="A85" s="7" t="s">
+    <row r="117" spans="1:2">
+      <c r="A117" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="B85" s="7" t="s">
+      <c r="B117" s="5" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
-      <c r="A86" s="7" t="s">
+    <row r="118" spans="1:2">
+      <c r="A118" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="B86" s="7" t="s">
+      <c r="B118" s="5" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
-      <c r="A87" s="7" t="s">
+    <row r="119" spans="1:2">
+      <c r="A119" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="B87" s="7" t="s">
+      <c r="B119" s="5" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
-      <c r="A88" s="7" t="s">
+    <row r="120" spans="1:2">
+      <c r="A120" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B120" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="B88" s="7" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
-      <c r="A89" s="7" t="s">
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B89" s="7" t="s">
+      <c r="B121" s="5" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
-      <c r="A90" s="7" t="s">
+    <row r="122" spans="1:2">
+      <c r="A122" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="B90" s="7" t="s">
+      <c r="B122" s="5" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
-      <c r="A91" s="7" t="s">
+    <row r="123" spans="1:2">
+      <c r="A123" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="B91" s="7" t="s">
+      <c r="B123" s="5" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
-      <c r="A92" s="7" t="s">
+    <row r="124" spans="1:2">
+      <c r="A124" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="B92" s="7" t="s">
+      <c r="B124" s="5" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
-      <c r="A93" s="7" t="s">
+    <row r="125" spans="1:2">
+      <c r="A125" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="B93" s="7" t="s">
+      <c r="B125" s="5" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
-      <c r="A94" s="7" t="s">
+    <row r="126" spans="1:2">
+      <c r="A126" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="B94" s="7" t="s">
+      <c r="B126" s="5" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
-      <c r="A95" s="7" t="s">
+    <row r="127" spans="1:2">
+      <c r="A127" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="B95" s="7" t="s">
+      <c r="B127" s="5" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
-      <c r="A96" s="7" t="s">
+    <row r="128" spans="1:2">
+      <c r="A128" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="B128" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="B96" s="7" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2">
-      <c r="A97" s="7" t="s">
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="B97" s="7" t="s">
+      <c r="B129" s="5" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
-      <c r="A98" s="7" t="s">
+    <row r="130" spans="1:2">
+      <c r="A130" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="B98" s="7" t="s">
+      <c r="B130" s="5" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
-      <c r="A99" s="7" t="s">
+    <row r="131" spans="1:2">
+      <c r="A131" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="B99" s="7" t="s">
+      <c r="B131" s="5" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
-      <c r="A100" s="7" t="s">
+    <row r="132" spans="1:2">
+      <c r="A132" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="B100" s="7" t="s">
+      <c r="B132" s="5" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
-      <c r="A101" s="7" t="s">
+    <row r="133" spans="1:2">
+      <c r="A133" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="B101" s="7" t="s">
+      <c r="B133" s="5" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
-      <c r="A102" s="7" t="s">
+    <row r="134" spans="1:2">
+      <c r="A134" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="B102" s="7" t="s">
+      <c r="B134" s="5" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
-      <c r="A103" s="7" t="s">
+    <row r="135" spans="1:2">
+      <c r="A135" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="B103" s="7" t="s">
+      <c r="B135" s="5" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
-      <c r="A104" s="7" t="s">
+    <row r="136" spans="1:2">
+      <c r="A136" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="B104" s="7" t="s">
+      <c r="B136" s="5" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
-      <c r="A105" s="7" t="s">
+    <row r="137" spans="1:2">
+      <c r="A137" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="B105" s="7" t="s">
+      <c r="B137" s="5" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
-      <c r="A106" s="7" t="s">
+    <row r="138" spans="1:2">
+      <c r="A138" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="B138" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="B106" s="7" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2">
-      <c r="A107" s="7" t="s">
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="B107" s="7" t="s">
+      <c r="B139" s="5" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="108" spans="1:2">
-      <c r="A108" s="7" t="s">
+    <row r="140" spans="1:2">
+      <c r="A140" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="B108" s="7" t="s">
+      <c r="B140" s="5" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="109" spans="1:2">
-      <c r="A109" s="7" t="s">
+    <row r="141" spans="1:2">
+      <c r="A141" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="B109" s="7" t="s">
+      <c r="B141" s="5" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="110" spans="1:2">
-      <c r="A110" s="7" t="s">
+    <row r="142" spans="1:2">
+      <c r="A142" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="B110" s="7" t="s">
+      <c r="B142" s="5" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="111" spans="1:2">
-      <c r="A111" s="7" t="s">
+    <row r="143" spans="1:2">
+      <c r="A143" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="B111" s="7" t="s">
+      <c r="B143" s="5" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="112" spans="1:2">
-      <c r="A112" s="7" t="s">
+    <row r="144" spans="1:2">
+      <c r="A144" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="B112" s="7" t="s">
+      <c r="B144" s="5" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="113" spans="1:2">
-      <c r="A113" s="7" t="s">
+    <row r="145" spans="1:2">
+      <c r="A145" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="B113" s="7" t="s">
+      <c r="B145" s="5" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="114" spans="1:2">
-      <c r="A114" s="7" t="s">
+    <row r="146" spans="1:2">
+      <c r="A146" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="B114" s="7" t="s">
+      <c r="B146" s="5" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="115" spans="1:2">
-      <c r="A115" s="7" t="s">
+    <row r="147" spans="1:2">
+      <c r="A147" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="B115" s="7" t="s">
+      <c r="B147" s="5" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="116" spans="1:2">
-      <c r="A116" s="7" t="s">
+    <row r="148" spans="1:2">
+      <c r="A148" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="B116" s="7" t="s">
+      <c r="B148" s="5" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="117" spans="1:2">
-      <c r="A117" s="7" t="s">
+    <row r="149" spans="1:2">
+      <c r="A149" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="B149" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="B117" s="7" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2">
-      <c r="A118" s="7" t="s">
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="B118" s="7" t="s">
+      <c r="B150" s="5" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="119" spans="1:2">
-      <c r="A119" s="7" t="s">
+    <row r="151" spans="1:2">
+      <c r="A151" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="B119" s="7" t="s">
+      <c r="B151" s="5" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="120" spans="1:2">
-      <c r="A120" s="7" t="s">
+    <row r="152" spans="1:2">
+      <c r="A152" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="B120" s="7" t="s">
+      <c r="B152" s="5" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="121" spans="1:2">
-      <c r="A121" s="7" t="s">
+    <row r="153" spans="1:2">
+      <c r="A153" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="B121" s="7" t="s">
+      <c r="B153" s="5" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="122" spans="1:2">
-      <c r="A122" s="7" t="s">
+    <row r="154" spans="1:2">
+      <c r="A154" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="B122" s="7" t="s">
+      <c r="B154" s="5" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="123" spans="1:2">
-      <c r="A123" s="7" t="s">
+    <row r="155" spans="1:2">
+      <c r="A155" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="B123" s="7" t="s">
+      <c r="B155" s="5" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="124" spans="1:2">
-      <c r="A124" s="7" t="s">
+    <row r="156" spans="1:2">
+      <c r="A156" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="B124" s="7" t="s">
+      <c r="B156" s="5" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="125" spans="1:2">
-      <c r="A125" s="7" t="s">
+    <row r="157" spans="1:2">
+      <c r="A157" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="B125" s="7" t="s">
+      <c r="B157" s="5" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="126" spans="1:2">
-      <c r="A126" s="7" t="s">
+    <row r="158" spans="1:2">
+      <c r="A158" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="B126" s="7" t="s">
+      <c r="B158" s="5" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="127" spans="1:2">
-      <c r="A127" s="7" t="s">
+    <row r="159" spans="1:2">
+      <c r="A159" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="B127" s="7" t="s">
+      <c r="B159" s="5" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="128" spans="1:2">
-      <c r="A128" s="7" t="s">
+    <row r="160" spans="1:2">
+      <c r="A160" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B160" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="B128" s="7" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2">
-      <c r="A129" s="7" t="s">
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="B129" s="7" t="s">
+      <c r="B161" s="5" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="130" spans="1:2">
-      <c r="A130" s="7" t="s">
+    <row r="162" spans="1:2">
+      <c r="A162" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="B130" s="7" t="s">
+      <c r="B162" s="5" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="131" spans="1:2">
-      <c r="A131" s="7" t="s">
+    <row r="163" spans="1:2">
+      <c r="A163" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B131" s="7" t="s">
+      <c r="B163" s="5" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="132" spans="1:2">
-      <c r="A132" s="7" t="s">
+    <row r="164" spans="1:2">
+      <c r="A164" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="B132" s="7" t="s">
+      <c r="B164" s="5" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="133" spans="1:2">
-      <c r="A133" s="7" t="s">
+    <row r="165" spans="1:2">
+      <c r="A165" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="B133" s="7" t="s">
+      <c r="B165" s="5" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="134" spans="1:2">
-      <c r="A134" s="7" t="s">
+    <row r="166" spans="1:2">
+      <c r="A166" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="B134" s="7" t="s">
+      <c r="B166" s="5" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="135" spans="1:2">
-      <c r="A135" s="7" t="s">
+    <row r="167" spans="1:2">
+      <c r="A167" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="B135" s="7" t="s">
+      <c r="B167" s="5" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="136" spans="1:2">
-      <c r="A136" s="7" t="s">
+    <row r="168" spans="1:2">
+      <c r="A168" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="B136" s="7" t="s">
+      <c r="B168" s="5" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="137" spans="1:2">
-      <c r="A137" s="7" t="s">
+    <row r="169" spans="1:2">
+      <c r="A169" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="B137" s="7" t="s">
+      <c r="B169" s="5" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="138" spans="1:2">
-      <c r="A138" s="7" t="s">
+    <row r="170" spans="1:2">
+      <c r="A170" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="B138" s="7" t="s">
+      <c r="B170" s="5" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="139" spans="1:2">
-      <c r="A139" s="7" t="s">
+    <row r="171" spans="1:2">
+      <c r="A171" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="B139" s="7" t="s">
+      <c r="B171" s="5" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="140" spans="1:2">
-      <c r="A140" s="7" t="s">
+    <row r="172" spans="1:2">
+      <c r="A172" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="B140" s="7" t="s">
+      <c r="B172" s="5" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="141" spans="1:2">
-      <c r="A141" s="7" t="s">
+    <row r="173" spans="1:2">
+      <c r="A173" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="B141" s="7" t="s">
+      <c r="B173" s="5" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="142" spans="1:2">
-      <c r="A142" s="7" t="s">
+    <row r="174" spans="1:2">
+      <c r="A174" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="B142" s="7" t="s">
+      <c r="B174" s="5" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="143" spans="1:2">
-      <c r="A143" s="7" t="s">
+    <row r="175" spans="1:2">
+      <c r="A175" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="B143" s="7" t="s">
+      <c r="B175" s="5" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="144" spans="1:2">
-      <c r="A144" s="7" t="s">
+    <row r="176" spans="1:2">
+      <c r="A176" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="B144" s="7" t="s">
+      <c r="B176" s="5" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="145" spans="1:2">
-      <c r="A145" s="7" t="s">
+    <row r="177" spans="1:2">
+      <c r="A177" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="B145" s="7" t="s">
+      <c r="B177" s="5" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="146" spans="1:2">
-      <c r="A146" s="7" t="s">
+    <row r="178" spans="1:2">
+      <c r="A178" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="B146" s="7" t="s">
+      <c r="B178" s="5" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="147" spans="1:2">
-      <c r="A147" s="7" t="s">
+    <row r="179" spans="1:2">
+      <c r="A179" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="B147" s="7" t="s">
+      <c r="B179" s="5" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="148" spans="1:2">
-      <c r="A148" s="7" t="s">
+    <row r="180" spans="1:2">
+      <c r="A180" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="B148" s="7" t="s">
+      <c r="B180" s="5" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="149" spans="1:2">
-      <c r="A149" s="7" t="s">
+    <row r="181" spans="1:2">
+      <c r="A181" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="B149" s="7" t="s">
+      <c r="B181" s="5" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="150" spans="1:2">
-      <c r="A150" s="7" t="s">
+    <row r="182" spans="1:2">
+      <c r="A182" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="B150" s="7" t="s">
+      <c r="B182" s="5" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="151" spans="1:2">
-      <c r="A151" s="7" t="s">
+    <row r="183" spans="1:2">
+      <c r="A183" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="B151" s="7" t="s">
+      <c r="B183" s="5" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="152" spans="1:2">
-      <c r="A152" s="7" t="s">
+    <row r="184" spans="1:2">
+      <c r="A184" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="B152" s="7" t="s">
+      <c r="B184" s="5" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="153" spans="1:2">
-      <c r="A153" s="7" t="s">
+    <row r="185" spans="1:2">
+      <c r="A185" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="B153" s="7" t="s">
+      <c r="B185" s="5" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="154" spans="1:2">
-      <c r="A154" s="7" t="s">
+    <row r="186" spans="1:2">
+      <c r="A186" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="B154" s="7" t="s">
+      <c r="B186" s="5" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="155" spans="1:2">
-      <c r="A155" s="7" t="s">
+    <row r="187" spans="1:2">
+      <c r="A187" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="B155" s="7" t="s">
+      <c r="B187" s="5" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="156" spans="1:2">
-      <c r="A156" s="7" t="s">
+    <row r="188" spans="1:2">
+      <c r="A188" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="B156" s="7" t="s">
+      <c r="B188" s="5" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="157" spans="1:2">
-      <c r="A157" s="7" t="s">
+    <row r="189" spans="1:2">
+      <c r="A189" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="B157" s="7" t="s">
+      <c r="B189" s="5" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="158" spans="1:2">
-      <c r="A158" s="7" t="s">
+    <row r="190" spans="1:2">
+      <c r="A190" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="B158" s="7" t="s">
+      <c r="B190" s="5" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="159" spans="1:2">
-      <c r="A159" s="7" t="s">
+    <row r="191" spans="1:2">
+      <c r="A191" s="5" t="s">
         <v>373</v>
       </c>
-      <c r="B159" s="7" t="s">
+      <c r="B191" s="5" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="160" spans="1:2">
-      <c r="A160" s="7" t="s">
+    <row r="192" spans="1:2">
+      <c r="A192" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="B192" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="B160" s="7" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2">
-      <c r="A161" s="7" t="s">
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="5" t="s">
         <v>377</v>
       </c>
-      <c r="B161" s="7" t="s">
+      <c r="B193" s="5" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="162" spans="1:2">
-      <c r="A162" s="7" t="s">
+    <row r="194" spans="1:2">
+      <c r="A194" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="B162" s="7" t="s">
+      <c r="B194" s="5" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="163" spans="1:2">
-      <c r="A163" s="7" t="s">
+    <row r="195" spans="1:2">
+      <c r="A195" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="B163" s="7" t="s">
+      <c r="B195" s="5" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="164" spans="1:2">
-      <c r="A164" s="7" t="s">
+    <row r="196" spans="1:2">
+      <c r="A196" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="B164" s="7" t="s">
+      <c r="B196" s="5" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="165" spans="1:2">
-      <c r="A165" s="7" t="s">
+    <row r="197" spans="1:2">
+      <c r="A197" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="B165" s="7" t="s">
+      <c r="B197" s="5" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="166" spans="1:2">
-      <c r="A166" s="7" t="s">
+    <row r="198" spans="1:2">
+      <c r="A198" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="B166" s="7" t="s">
+      <c r="B198" s="5" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="167" spans="1:2">
-      <c r="A167" s="7" t="s">
+    <row r="199" spans="1:2">
+      <c r="A199" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="B199" s="5" t="s">
         <v>389</v>
       </c>
-      <c r="B167" s="7" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2">
-      <c r="A168" s="7" t="s">
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="B168" s="7" t="s">
+      <c r="B200" s="5" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="169" spans="1:2">
-      <c r="A169" s="7" t="s">
+    <row r="201" spans="1:2">
+      <c r="A201" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="B169" s="7" t="s">
+      <c r="B201" s="5" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="170" spans="1:2">
-      <c r="A170" s="7" t="s">
+    <row r="202" spans="1:2">
+      <c r="A202" s="5" t="s">
         <v>395</v>
       </c>
-      <c r="B170" s="7" t="s">
+      <c r="B202" s="5" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="171" spans="1:2">
-      <c r="A171" s="7" t="s">
+    <row r="203" spans="1:2">
+      <c r="A203" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="B171" s="7" t="s">
+      <c r="B203" s="5" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="172" spans="1:2">
-      <c r="A172" s="7" t="s">
+    <row r="204" spans="1:2">
+      <c r="A204" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="B172" s="7" t="s">
+      <c r="B204" s="5" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="173" spans="1:2">
-      <c r="A173" s="7" t="s">
+    <row r="205" spans="1:2">
+      <c r="A205" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="B173" s="7" t="s">
+      <c r="B205" s="5" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="174" spans="1:2">
-      <c r="A174" s="7" t="s">
+    <row r="206" spans="1:2" ht="15.5">
+      <c r="A206" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="B174" s="7" t="s">
+      <c r="B206" s="1" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="175" spans="1:2">
-      <c r="A175" s="7" t="s">
+    <row r="207" spans="1:2">
+      <c r="A207" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="B175" s="7" t="s">
+      <c r="B207" s="5" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="176" spans="1:2">
-      <c r="A176" s="7" t="s">
+    <row r="208" spans="1:2" ht="15.5">
+      <c r="A208" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B176" s="7" t="s">
+      <c r="B208" s="1" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="177" spans="1:2">
-      <c r="A177" s="7" t="s">
+    <row r="209" spans="1:2" ht="15.5">
+      <c r="A209" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="B177" s="7" t="s">
+      <c r="B209" s="1" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="178" spans="1:2">
-      <c r="A178" s="7" t="s">
+    <row r="210" spans="1:2">
+      <c r="A210" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="B178" s="7" t="s">
+      <c r="B210" s="5" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="179" spans="1:2">
-      <c r="A179" s="7" t="s">
+    <row r="211" spans="1:2">
+      <c r="A211" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="B179" s="7" t="s">
+      <c r="B211" s="5" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="180" spans="1:2">
-      <c r="A180" s="7" t="s">
+    <row r="212" spans="1:2">
+      <c r="A212" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="B180" s="7" t="s">
+      <c r="B212" s="5" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="181" spans="1:2">
-      <c r="A181" s="7" t="s">
+    <row r="213" spans="1:2">
+      <c r="A213" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="B181" s="7" t="s">
+      <c r="B213" s="5" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="182" spans="1:2">
-      <c r="A182" s="7" t="s">
+    <row r="214" spans="1:2">
+      <c r="A214" s="7" t="s">
         <v>419</v>
       </c>
-      <c r="B182" s="7" t="s">
+      <c r="B214" s="7" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="183" spans="1:2">
-      <c r="A183" s="7" t="s">
+    <row r="215" spans="1:2">
+      <c r="A215" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="B183" s="7" t="s">
+      <c r="B215" s="5" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="184" spans="1:2">
-      <c r="A184" s="7" t="s">
+    <row r="216" spans="1:2">
+      <c r="A216" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="B184" s="7" t="s">
+      <c r="B216" s="5" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="185" spans="1:2">
-      <c r="A185" s="7" t="s">
+    <row r="217" spans="1:2" ht="18">
+      <c r="A217" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B185" s="7" t="s">
+      <c r="B217" s="2" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="186" spans="1:2">
-      <c r="A186" s="7" t="s">
+    <row r="218" spans="1:2">
+      <c r="A218" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="B186" s="7" t="s">
+      <c r="B218" s="5" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="187" spans="1:2">
-      <c r="A187" s="7" t="s">
+    <row r="219" spans="1:2">
+      <c r="A219" s="7" t="s">
         <v>429</v>
       </c>
-      <c r="B187" s="7" t="s">
+      <c r="B219" s="7" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="188" spans="1:2">
-      <c r="A188" s="7" t="s">
+    <row r="220" spans="1:2">
+      <c r="A220" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="B188" s="7" t="s">
+      <c r="B220" s="5" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="189" spans="1:2">
-      <c r="A189" s="7" t="s">
+    <row r="221" spans="1:2">
+      <c r="A221" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="B189" s="7" t="s">
+      <c r="B221" s="7" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="190" spans="1:2">
-      <c r="A190" s="7" t="s">
+    <row r="222" spans="1:2">
+      <c r="A222" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="B222" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="B190" s="7" t="s">
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" s="5" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="191" spans="1:2">
-      <c r="A191" s="7" t="s">
+      <c r="B223" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="B191" s="7" t="s">
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" s="5" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="192" spans="1:2">
-      <c r="A192" s="7" t="s">
+      <c r="B224" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="B192" s="7" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2">
-      <c r="A193" s="7" t="s">
+      <c r="B225" s="5" t="s">
         <v>442</v>
       </c>
-      <c r="B193" s="7" t="s">
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" s="5" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="194" spans="1:2">
-      <c r="A194" s="7" t="s">
+      <c r="B226" s="5" t="s">
         <v>444</v>
       </c>
-      <c r="B194" s="7" t="s">
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" s="7" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="195" spans="1:2">
-      <c r="A195" s="7" t="s">
+      <c r="B227" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="B195" s="7" t="s">
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" s="5" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="196" spans="1:2">
-      <c r="A196" s="7" t="s">
+      <c r="B228" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="B196" s="7" t="s">
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" s="7" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="197" spans="1:2">
-      <c r="A197" s="7" t="s">
+      <c r="B229" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="B197" s="7" t="s">
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" s="5" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="198" spans="1:2">
-      <c r="A198" s="7" t="s">
+      <c r="B230" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="B198" s="7" t="s">
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" s="5" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="199" spans="1:2">
-      <c r="A199" s="7" t="s">
+      <c r="B231" s="5" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="B199" s="7" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2">
-      <c r="A200" s="7" t="s">
+      <c r="B232" s="7" t="s">
         <v>456</v>
       </c>
-      <c r="B200" s="7" t="s">
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" s="7" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="201" spans="1:2">
-      <c r="A201" s="7" t="s">
+      <c r="B233" s="7" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" s="5" t="s">
         <v>459</v>
       </c>
-      <c r="B201" s="7" t="s">
+      <c r="B234" s="5" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="202" spans="1:2">
-      <c r="A202" s="7" t="s">
+    <row r="235" spans="1:2">
+      <c r="A235" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="B202" s="7" t="s">
+      <c r="B235" s="5" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="203" spans="1:2">
-      <c r="A203" s="7" t="s">
+    <row r="236" spans="1:2">
+      <c r="A236" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="B203" s="7" t="s">
+      <c r="B236" s="7" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="204" spans="1:2">
-      <c r="A204" s="7" t="s">
+    <row r="237" spans="1:2">
+      <c r="A237" s="7" t="s">
         <v>465</v>
       </c>
-      <c r="B204" s="7" t="s">
+      <c r="B237" s="7" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="B238" s="5" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="205" spans="1:2">
-      <c r="A205" s="7" t="s">
+    <row r="239" spans="1:2">
+      <c r="A239" s="7" t="s">
         <v>469</v>
       </c>
-      <c r="B205" s="7" t="s">
+      <c r="B239" s="7" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="206" spans="1:2" ht="15.5">
-      <c r="A206" s="3" t="s">
+    <row r="240" spans="1:2">
+      <c r="A240" s="7" t="s">
         <v>471</v>
       </c>
-      <c r="B206" s="3" t="s">
+      <c r="B240" s="7" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="207" spans="1:2">
-      <c r="A207" s="7" t="s">
+    <row r="241" spans="1:2">
+      <c r="A241" s="7" t="s">
         <v>473</v>
       </c>
-      <c r="B207" s="7" t="s">
+      <c r="B241" s="7" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="208" spans="1:2" ht="15.5">
-      <c r="A208" s="3" t="s">
+    <row r="242" spans="1:2">
+      <c r="A242" s="5" t="s">
         <v>475</v>
       </c>
-      <c r="B208" s="3" t="s">
+      <c r="B242" s="5" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="209" spans="1:2" ht="15.5">
-      <c r="A209" s="3" t="s">
+    <row r="243" spans="1:2">
+      <c r="A243" s="7" t="s">
         <v>477</v>
       </c>
-      <c r="B209" s="3" t="s">
+      <c r="B243" s="7" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="210" spans="1:2">
-      <c r="A210" s="7" t="s">
+    <row r="244" spans="1:2">
+      <c r="A244" s="7" t="s">
         <v>479</v>
       </c>
-      <c r="B210" s="7" t="s">
+      <c r="B244" s="7" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="211" spans="1:2">
-      <c r="A211" s="7" t="s">
+    <row r="245" spans="1:2">
+      <c r="A245" s="5" t="s">
         <v>481</v>
       </c>
-      <c r="B211" s="7" t="s">
+      <c r="B245" s="5" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="212" spans="1:2">
-      <c r="A212" s="7" t="s">
+    <row r="246" spans="1:2">
+      <c r="A246" s="5" t="s">
         <v>483</v>
       </c>
-      <c r="B212" s="7" t="s">
+      <c r="B246" s="5" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="213" spans="1:2">
-      <c r="A213" s="7" t="s">
+    <row r="247" spans="1:2">
+      <c r="A247" s="7" t="s">
         <v>485</v>
       </c>
-      <c r="B213" s="7" t="s">
+      <c r="B247" s="7" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="214" spans="1:2">
-      <c r="A214" s="9" t="s">
+    <row r="248" spans="1:2">
+      <c r="A248" s="5" t="s">
         <v>487</v>
       </c>
-      <c r="B214" s="9" t="s">
+      <c r="B248" s="5" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="215" spans="1:2">
-      <c r="A215" s="7" t="s">
+    <row r="249" spans="1:2">
+      <c r="A249" s="5" t="s">
         <v>489</v>
       </c>
-      <c r="B215" s="7" t="s">
+      <c r="B249" s="5" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="216" spans="1:2">
-      <c r="A216" s="7" t="s">
+    <row r="250" spans="1:2">
+      <c r="A250" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="B250" s="5" t="s">
         <v>491</v>
       </c>
-      <c r="B216" s="7" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2" ht="18">
-      <c r="A217" s="4" t="s">
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251" s="7" t="s">
         <v>493</v>
       </c>
-      <c r="B217" s="4" t="s">
+      <c r="B251" s="7" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="218" spans="1:2">
-      <c r="A218" s="7" t="s">
+    <row r="252" spans="1:2">
+      <c r="A252" s="7" t="s">
         <v>495</v>
       </c>
-      <c r="B218" s="7" t="s">
+      <c r="B252" s="7" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="219" spans="1:2">
-      <c r="A219" s="9" t="s">
+    <row r="253" spans="1:2">
+      <c r="A253" s="5" t="s">
         <v>497</v>
       </c>
-      <c r="B219" s="9" t="s">
+      <c r="B253" s="5" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="220" spans="1:2">
-      <c r="A220" s="7" t="s">
+    <row r="254" spans="1:2">
+      <c r="A254" s="7" t="s">
         <v>499</v>
       </c>
-      <c r="B220" s="7" t="s">
+      <c r="B254" s="7" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="221" spans="1:2">
-      <c r="A221" s="9" t="s">
+    <row r="255" spans="1:2">
+      <c r="A255" s="5" t="s">
         <v>501</v>
       </c>
-      <c r="B221" s="9" t="s">
+      <c r="B255" s="5" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="222" spans="1:2">
-      <c r="A222" s="7" t="s">
+    <row r="256" spans="1:2">
+      <c r="A256" s="7" t="s">
         <v>503</v>
       </c>
-      <c r="B222" s="7" t="s">
+      <c r="B256" s="7" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="223" spans="1:2">
-      <c r="A223" s="7" t="s">
+    <row r="257" spans="1:2">
+      <c r="A257" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="B223" s="7" t="s">
+      <c r="B257" s="7" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="224" spans="1:2">
-      <c r="A224" s="7" t="s">
+    <row r="258" spans="1:2">
+      <c r="A258" s="7" t="s">
         <v>507</v>
       </c>
-      <c r="B224" s="7" t="s">
+      <c r="B258" s="7" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="225" spans="1:2">
-      <c r="A225" s="7" t="s">
+    <row r="259" spans="1:2">
+      <c r="A259" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="B259" s="7" t="s">
         <v>509</v>
       </c>
-      <c r="B225" s="7" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="226" spans="1:2">
-      <c r="A226" s="7" t="s">
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" s="7" t="s">
         <v>511</v>
       </c>
-      <c r="B226" s="7" t="s">
+      <c r="B260" s="7" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="227" spans="1:2">
-      <c r="A227" s="9" t="s">
+    <row r="261" spans="1:2">
+      <c r="A261" s="7" t="s">
         <v>513</v>
       </c>
-      <c r="B227" s="9" t="s">
+      <c r="B261" s="7" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="228" spans="1:2">
-      <c r="A228" s="7" t="s">
+    <row r="262" spans="1:2">
+      <c r="A262" s="7" t="s">
         <v>515</v>
       </c>
-      <c r="B228" s="7" t="s">
+      <c r="B262" s="7" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="229" spans="1:2">
-      <c r="A229" s="9" t="s">
+    <row r="263" spans="1:2">
+      <c r="A263" s="7" t="s">
         <v>517</v>
       </c>
-      <c r="B229" s="9" t="s">
+      <c r="B263" s="7" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="230" spans="1:2">
-      <c r="A230" s="7" t="s">
+    <row r="264" spans="1:2">
+      <c r="A264" s="5" t="s">
         <v>519</v>
       </c>
-      <c r="B230" s="7" t="s">
+      <c r="B264" s="5" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="231" spans="1:2">
-      <c r="A231" s="7" t="s">
+    <row r="265" spans="1:2">
+      <c r="A265" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B231" s="7" t="s">
+      <c r="B265" s="5" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="232" spans="1:2">
-      <c r="A232" s="9" t="s">
+    <row r="266" spans="1:2">
+      <c r="A266" s="7" t="s">
         <v>523</v>
       </c>
-      <c r="B232" s="9" t="s">
+      <c r="B266" s="7" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="233" spans="1:2">
-      <c r="A233" s="9" t="s">
-        <v>525</v>
-      </c>
-      <c r="B233" s="9" t="s">
+    <row r="267" spans="1:2">
+      <c r="A267" s="3" t="s">
         <v>526</v>
       </c>
-    </row>
-    <row r="234" spans="1:2">
-      <c r="A234" s="7" t="s">
+      <c r="B267" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="B234" s="7" t="s">
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" s="5" t="s">
         <v>528</v>
       </c>
-    </row>
-    <row r="235" spans="1:2">
-      <c r="A235" s="7" t="s">
+      <c r="B268" s="5" t="s">
         <v>529</v>
-      </c>
-      <c r="B235" s="7" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="236" spans="1:2">
-      <c r="A236" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="B236" s="9" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="237" spans="1:2">
-      <c r="A237" s="9" t="s">
-        <v>533</v>
-      </c>
-      <c r="B237" s="9" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="238" spans="1:2">
-      <c r="A238" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="B238" s="7" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="239" spans="1:2">
-      <c r="A239" s="9" t="s">
-        <v>537</v>
-      </c>
-      <c r="B239" s="9" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="240" spans="1:2">
-      <c r="A240" s="9" t="s">
-        <v>539</v>
-      </c>
-      <c r="B240" s="9" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="241" spans="1:2">
-      <c r="A241" s="9" t="s">
-        <v>541</v>
-      </c>
-      <c r="B241" s="9" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="242" spans="1:2">
-      <c r="A242" s="7" t="s">
-        <v>543</v>
-      </c>
-      <c r="B242" s="7" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="243" spans="1:2">
-      <c r="A243" s="9" t="s">
-        <v>545</v>
-      </c>
-      <c r="B243" s="9" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="244" spans="1:2">
-      <c r="A244" s="9" t="s">
-        <v>547</v>
-      </c>
-      <c r="B244" s="9" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="245" spans="1:2">
-      <c r="A245" s="7" t="s">
-        <v>549</v>
-      </c>
-      <c r="B245" s="7" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="246" spans="1:2">
-      <c r="A246" s="7" t="s">
-        <v>551</v>
-      </c>
-      <c r="B246" s="7" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="247" spans="1:2">
-      <c r="A247" s="9" t="s">
-        <v>553</v>
-      </c>
-      <c r="B247" s="9" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="248" spans="1:2">
-      <c r="A248" s="7" t="s">
-        <v>555</v>
-      </c>
-      <c r="B248" s="7" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="249" spans="1:2">
-      <c r="A249" s="7" t="s">
-        <v>557</v>
-      </c>
-      <c r="B249" s="7" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="250" spans="1:2">
-      <c r="A250" s="7" t="s">
-        <v>560</v>
-      </c>
-      <c r="B250" s="7" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="251" spans="1:2">
-      <c r="A251" s="9" t="s">
-        <v>561</v>
-      </c>
-      <c r="B251" s="9" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="252" spans="1:2">
-      <c r="A252" s="9" t="s">
-        <v>563</v>
-      </c>
-      <c r="B252" s="9" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="253" spans="1:2">
-      <c r="A253" s="7" t="s">
-        <v>565</v>
-      </c>
-      <c r="B253" s="7" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="254" spans="1:2">
-      <c r="A254" s="9" t="s">
-        <v>567</v>
-      </c>
-      <c r="B254" s="9" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="255" spans="1:2">
-      <c r="A255" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="B255" s="7" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="256" spans="1:2">
-      <c r="A256" s="9" t="s">
-        <v>571</v>
-      </c>
-      <c r="B256" s="9" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="257" spans="1:2">
-      <c r="A257" s="9" t="s">
-        <v>573</v>
-      </c>
-      <c r="B257" s="9" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="258" spans="1:2">
-      <c r="A258" s="9" t="s">
-        <v>575</v>
-      </c>
-      <c r="B258" s="9" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="259" spans="1:2">
-      <c r="A259" s="9" t="s">
-        <v>578</v>
-      </c>
-      <c r="B259" s="9" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="260" spans="1:2">
-      <c r="A260" s="9" t="s">
-        <v>579</v>
-      </c>
-      <c r="B260" s="9" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="261" spans="1:2">
-      <c r="A261" s="9" t="s">
-        <v>581</v>
-      </c>
-      <c r="B261" s="9" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="262" spans="1:2">
-      <c r="A262" s="9" t="s">
-        <v>583</v>
-      </c>
-      <c r="B262" s="9" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="263" spans="1:2">
-      <c r="A263" s="9" t="s">
-        <v>585</v>
-      </c>
-      <c r="B263" s="9" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="264" spans="1:2">
-      <c r="A264" s="7" t="s">
-        <v>587</v>
-      </c>
-      <c r="B264" s="7" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="265" spans="1:2">
-      <c r="A265" s="7" t="s">
-        <v>589</v>
-      </c>
-      <c r="B265" s="7" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="266" spans="1:2">
-      <c r="A266" s="9" t="s">
-        <v>591</v>
-      </c>
-      <c r="B266" s="9" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="267" spans="1:2">
-      <c r="A267" s="5" t="s">
-        <v>596</v>
-      </c>
-      <c r="B267" s="5" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="268" spans="1:2">
-      <c r="A268" s="7" t="s">
-        <v>598</v>
-      </c>
-      <c r="B268" s="7" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="269" spans="1:2">
       <c r="A269" t="s">
-        <v>600</v>
+        <v>530</v>
       </c>
       <c r="B269" t="s">
-        <v>601</v>
+        <v>531</v>
       </c>
     </row>
     <row r="270" spans="1:2">
       <c r="A270" t="s">
-        <v>602</v>
+        <v>532</v>
       </c>
       <c r="B270" t="s">
-        <v>603</v>
+        <v>533</v>
       </c>
     </row>
     <row r="271" spans="1:2">
       <c r="A271" t="s">
-        <v>604</v>
+        <v>534</v>
       </c>
       <c r="B271" t="s">
-        <v>605</v>
+        <v>535</v>
       </c>
     </row>
     <row r="272" spans="1:2">
-      <c r="A272" s="5" t="s">
-        <v>606</v>
-      </c>
-      <c r="B272" s="5" t="s">
-        <v>607</v>
+      <c r="A272" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="B272" s="3" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="273" spans="1:2">
       <c r="A273" t="s">
-        <v>608</v>
+        <v>538</v>
       </c>
       <c r="B273" t="s">
-        <v>609</v>
+        <v>539</v>
       </c>
     </row>
     <row r="274" spans="1:2">
       <c r="A274" t="s">
-        <v>610</v>
+        <v>540</v>
       </c>
       <c r="B274" t="s">
-        <v>611</v>
+        <v>541</v>
       </c>
     </row>
     <row r="275" spans="1:2">
-      <c r="A275" s="5" t="s">
-        <v>612</v>
-      </c>
-      <c r="B275" s="5" t="s">
-        <v>613</v>
+      <c r="A275" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="B275" s="3" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="276" spans="1:2">
-      <c r="A276" s="5" t="s">
-        <v>614</v>
-      </c>
-      <c r="B276" s="5" t="s">
-        <v>615</v>
+      <c r="A276" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="B276" s="3" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="277" spans="1:2">
       <c r="A277" t="s">
-        <v>616</v>
+        <v>546</v>
       </c>
       <c r="B277" t="s">
-        <v>617</v>
+        <v>547</v>
       </c>
     </row>
     <row r="278" spans="1:2">
       <c r="A278" t="s">
-        <v>618</v>
+        <v>548</v>
       </c>
       <c r="B278" t="s">
-        <v>619</v>
+        <v>549</v>
       </c>
     </row>
     <row r="279" spans="1:2">
-      <c r="A279" s="7" t="s">
-        <v>620</v>
-      </c>
-      <c r="B279" s="7" t="s">
-        <v>621</v>
+      <c r="A279" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="B279" s="5" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="280" spans="1:2">
       <c r="A280" t="s">
-        <v>622</v>
+        <v>552</v>
       </c>
       <c r="B280" t="s">
-        <v>623</v>
+        <v>553</v>
       </c>
     </row>
     <row r="281" spans="1:2">
       <c r="A281" t="s">
-        <v>624</v>
+        <v>554</v>
       </c>
       <c r="B281" t="s">
-        <v>625</v>
+        <v>555</v>
       </c>
     </row>
     <row r="282" spans="1:2">
-      <c r="A282" s="5" t="s">
-        <v>626</v>
-      </c>
-      <c r="B282" s="5" t="s">
-        <v>627</v>
+      <c r="A282" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B282" s="3" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="283" spans="1:2">
-      <c r="A283" s="5" t="s">
-        <v>628</v>
-      </c>
-      <c r="B283" s="5" t="s">
-        <v>629</v>
+      <c r="A283" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="B283" s="3" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="284" spans="1:2">
-      <c r="A284" s="5" t="s">
-        <v>630</v>
-      </c>
-      <c r="B284" s="5" t="s">
-        <v>631</v>
+      <c r="A284" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="B284" s="3" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="285" spans="1:2">
       <c r="A285" t="s">
-        <v>632</v>
+        <v>562</v>
       </c>
       <c r="B285" t="s">
-        <v>633</v>
+        <v>563</v>
       </c>
     </row>
     <row r="286" spans="1:2">
       <c r="A286" t="s">
-        <v>634</v>
+        <v>564</v>
       </c>
       <c r="B286" t="s">
-        <v>635</v>
+        <v>565</v>
       </c>
     </row>
     <row r="287" spans="1:2">
       <c r="A287" t="s">
-        <v>637</v>
+        <v>567</v>
       </c>
       <c r="B287" t="s">
-        <v>636</v>
+        <v>566</v>
       </c>
     </row>
     <row r="288" spans="1:2">
       <c r="A288" t="s">
-        <v>638</v>
+        <v>568</v>
       </c>
       <c r="B288" t="s">
-        <v>639</v>
+        <v>569</v>
       </c>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" t="s">
-        <v>640</v>
+        <v>570</v>
       </c>
       <c r="B289" t="s">
-        <v>641</v>
+        <v>571</v>
       </c>
     </row>
     <row r="290" spans="1:2">
-      <c r="A290" s="5" t="s">
-        <v>642</v>
-      </c>
-      <c r="B290" s="5" t="s">
-        <v>643</v>
+      <c r="A290" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="B290" s="3" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="291" spans="1:2">
-      <c r="A291" s="5" t="s">
-        <v>644</v>
-      </c>
-      <c r="B291" s="5" t="s">
-        <v>645</v>
+      <c r="A291" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="B291" s="3" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="292" spans="1:2">
-      <c r="A292" s="11" t="s">
-        <v>646</v>
-      </c>
-      <c r="B292" s="11" t="s">
-        <v>647</v>
+      <c r="A292" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="B292" s="9" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="293" spans="1:2">
-      <c r="A293" s="5" t="s">
-        <v>648</v>
-      </c>
-      <c r="B293" s="5" t="s">
-        <v>649</v>
+      <c r="A293" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="B293" s="3" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="294" spans="1:2">
-      <c r="A294" s="5" t="s">
-        <v>650</v>
-      </c>
-      <c r="B294" s="5" t="s">
-        <v>651</v>
+      <c r="A294" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="B294" s="3" t="s">
+        <v>581</v>
       </c>
     </row>
     <row r="295" spans="1:2">
-      <c r="A295" s="5" t="s">
-        <v>652</v>
-      </c>
-      <c r="B295" s="5" t="s">
-        <v>653</v>
+      <c r="A295" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="B295" s="3" t="s">
+        <v>583</v>
       </c>
     </row>
     <row r="296" spans="1:2">
-      <c r="A296" s="5" t="s">
-        <v>654</v>
-      </c>
-      <c r="B296" s="5" t="s">
-        <v>655</v>
+      <c r="A296" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="B296" s="3" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="297" spans="1:2">
-      <c r="A297" s="5" t="s">
-        <v>656</v>
-      </c>
-      <c r="B297" s="5" t="s">
-        <v>657</v>
+      <c r="A297" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="B297" s="3" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="298" spans="1:2">
-      <c r="A298" s="5" t="s">
-        <v>658</v>
-      </c>
-      <c r="B298" s="5" t="s">
-        <v>659</v>
+      <c r="A298" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="B298" s="3" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="299" spans="1:2">
       <c r="A299" t="s">
-        <v>660</v>
+        <v>590</v>
       </c>
       <c r="B299" t="s">
-        <v>661</v>
+        <v>591</v>
       </c>
     </row>
     <row r="300" spans="1:2">
       <c r="A300" t="s">
-        <v>662</v>
+        <v>592</v>
       </c>
       <c r="B300" t="s">
-        <v>663</v>
+        <v>593</v>
       </c>
     </row>
     <row r="301" spans="1:2">
       <c r="A301" t="s">
-        <v>664</v>
+        <v>594</v>
       </c>
       <c r="B301" t="s">
-        <v>665</v>
+        <v>595</v>
       </c>
     </row>
     <row r="302" spans="1:2">
       <c r="A302" t="s">
-        <v>666</v>
+        <v>596</v>
       </c>
       <c r="B302" t="s">
-        <v>667</v>
+        <v>597</v>
       </c>
     </row>
     <row r="303" spans="1:2">
-      <c r="A303" s="5" t="s">
-        <v>668</v>
-      </c>
-      <c r="B303" s="5" t="s">
-        <v>669</v>
+      <c r="A303" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="B303" s="3" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="304" spans="1:2">
       <c r="A304" t="s">
-        <v>670</v>
+        <v>600</v>
       </c>
       <c r="B304" t="s">
-        <v>671</v>
+        <v>601</v>
       </c>
     </row>
     <row r="305" spans="1:2">
-      <c r="A305" s="5" t="s">
-        <v>672</v>
-      </c>
-      <c r="B305" s="5" t="s">
-        <v>673</v>
+      <c r="A305" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="B305" s="3" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="306" spans="1:2">
       <c r="A306" t="s">
-        <v>674</v>
+        <v>604</v>
       </c>
       <c r="B306" t="s">
-        <v>675</v>
+        <v>605</v>
       </c>
     </row>
     <row r="307" spans="1:2">
-      <c r="A307" s="12" t="s">
-        <v>676</v>
-      </c>
-      <c r="B307" s="12" t="s">
-        <v>677</v>
+      <c r="A307" s="10" t="s">
+        <v>606</v>
+      </c>
+      <c r="B307" s="10" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="308" spans="1:2">
-      <c r="A308" s="12" t="s">
-        <v>678</v>
-      </c>
-      <c r="B308" s="12" t="s">
-        <v>679</v>
+      <c r="A308" s="10" t="s">
+        <v>608</v>
+      </c>
+      <c r="B308" s="10" t="s">
+        <v>609</v>
       </c>
     </row>
     <row r="309" spans="1:2">
       <c r="A309" t="s">
-        <v>680</v>
+        <v>610</v>
       </c>
       <c r="B309" t="s">
-        <v>681</v>
+        <v>611</v>
       </c>
     </row>
     <row r="310" spans="1:2">
       <c r="A310" t="s">
-        <v>682</v>
+        <v>612</v>
       </c>
       <c r="B310" t="s">
-        <v>683</v>
+        <v>613</v>
       </c>
     </row>
     <row r="311" spans="1:2">
       <c r="A311" t="s">
-        <v>684</v>
+        <v>614</v>
       </c>
       <c r="B311" t="s">
-        <v>685</v>
+        <v>615</v>
       </c>
     </row>
     <row r="312" spans="1:2">
       <c r="A312" t="s">
-        <v>686</v>
+        <v>616</v>
       </c>
       <c r="B312" t="s">
-        <v>687</v>
+        <v>617</v>
       </c>
     </row>
     <row r="313" spans="1:2">
-      <c r="A313" s="12" t="s">
-        <v>688</v>
-      </c>
-      <c r="B313" s="12" t="s">
-        <v>689</v>
+      <c r="A313" s="10" t="s">
+        <v>618</v>
+      </c>
+      <c r="B313" s="10" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="314" spans="1:2">
-      <c r="A314" s="5" t="s">
-        <v>690</v>
-      </c>
-      <c r="B314" s="5" t="s">
-        <v>691</v>
+      <c r="A314" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="B314" s="3" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="315" spans="1:2">
-      <c r="A315" s="5" t="s">
-        <v>692</v>
-      </c>
-      <c r="B315" s="5" t="s">
-        <v>693</v>
+      <c r="A315" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="B315" s="3" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="316" spans="1:2">
-      <c r="A316" s="5" t="s">
-        <v>694</v>
-      </c>
-      <c r="B316" s="5" t="s">
-        <v>695</v>
+      <c r="A316" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="B316" s="3" t="s">
+        <v>625</v>
       </c>
     </row>
     <row r="317" spans="1:2">
-      <c r="A317" s="12" t="s">
-        <v>696</v>
-      </c>
-      <c r="B317" s="12" t="s">
-        <v>697</v>
+      <c r="A317" s="10" t="s">
+        <v>626</v>
+      </c>
+      <c r="B317" s="10" t="s">
+        <v>627</v>
       </c>
     </row>
     <row r="318" spans="1:2">
       <c r="A318" t="s">
-        <v>698</v>
+        <v>628</v>
       </c>
       <c r="B318" t="s">
-        <v>699</v>
+        <v>629</v>
       </c>
     </row>
     <row r="319" spans="1:2">
-      <c r="A319" s="5" t="s">
-        <v>700</v>
-      </c>
-      <c r="B319" s="5" t="s">
-        <v>701</v>
+      <c r="A319" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="B319" s="3" t="s">
+        <v>631</v>
       </c>
     </row>
     <row r="320" spans="1:2">
-      <c r="A320" s="7" t="s">
-        <v>702</v>
-      </c>
-      <c r="B320" s="7" t="s">
-        <v>703</v>
+      <c r="A320" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="B320" s="5" t="s">
+        <v>633</v>
       </c>
     </row>
     <row r="321" spans="1:2">
-      <c r="A321" s="12" t="s">
-        <v>704</v>
-      </c>
-      <c r="B321" s="12" t="s">
-        <v>705</v>
+      <c r="A321" s="10" t="s">
+        <v>634</v>
+      </c>
+      <c r="B321" s="10" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="322" spans="1:2">
       <c r="A322" t="s">
-        <v>706</v>
+        <v>636</v>
       </c>
       <c r="B322" t="s">
-        <v>707</v>
+        <v>637</v>
       </c>
     </row>
     <row r="323" spans="1:2">
-      <c r="A323" s="5" t="s">
-        <v>708</v>
-      </c>
-      <c r="B323" s="5" t="s">
-        <v>709</v>
+      <c r="A323" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="B323" s="3" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="324" spans="1:2">
-      <c r="A324" s="5" t="s">
-        <v>710</v>
-      </c>
-      <c r="B324" s="5" t="s">
-        <v>711</v>
+      <c r="A324" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="B324" s="3" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="325" spans="1:2">
       <c r="A325" t="s">
-        <v>712</v>
+        <v>642</v>
       </c>
       <c r="B325" t="s">
-        <v>713</v>
+        <v>643</v>
       </c>
     </row>
     <row r="326" spans="1:2">
-      <c r="A326" s="5" t="s">
-        <v>714</v>
-      </c>
-      <c r="B326" s="5" t="s">
-        <v>715</v>
+      <c r="A326" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="B326" s="3" t="s">
+        <v>645</v>
       </c>
     </row>
     <row r="327" spans="1:2">
-      <c r="A327" s="7" t="s">
-        <v>716</v>
-      </c>
-      <c r="B327" s="7" t="s">
-        <v>717</v>
+      <c r="A327" s="5" t="s">
+        <v>646</v>
+      </c>
+      <c r="B327" s="5" t="s">
+        <v>647</v>
       </c>
     </row>
     <row r="328" spans="1:2">
-      <c r="A328" s="7" t="s">
-        <v>718</v>
-      </c>
-      <c r="B328" s="7" t="s">
-        <v>719</v>
+      <c r="A328" s="5" t="s">
+        <v>648</v>
+      </c>
+      <c r="B328" s="5" t="s">
+        <v>649</v>
       </c>
     </row>
     <row r="329" spans="1:2">
       <c r="A329" t="s">
-        <v>720</v>
+        <v>650</v>
       </c>
       <c r="B329" t="s">
-        <v>721</v>
+        <v>651</v>
       </c>
     </row>
     <row r="330" spans="1:2">
-      <c r="A330" s="5" t="s">
-        <v>722</v>
-      </c>
-      <c r="B330" s="5" t="s">
-        <v>723</v>
+      <c r="A330" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="B330" s="3" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="331" spans="1:2">
-      <c r="A331" s="7" t="s">
-        <v>724</v>
-      </c>
-      <c r="B331" s="7" t="s">
-        <v>725</v>
+      <c r="A331" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="B331" s="5" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="332" spans="1:2">
-      <c r="A332" s="5" t="s">
-        <v>726</v>
-      </c>
-      <c r="B332" s="5" t="s">
-        <v>727</v>
+      <c r="A332" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B332" s="3" t="s">
+        <v>657</v>
       </c>
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
-        <v>728</v>
+        <v>658</v>
       </c>
       <c r="B333" t="s">
-        <v>729</v>
+        <v>659</v>
       </c>
     </row>
     <row r="334" spans="1:2">
       <c r="A334" t="s">
-        <v>730</v>
+        <v>660</v>
       </c>
       <c r="B334" t="s">
-        <v>731</v>
+        <v>661</v>
       </c>
     </row>
     <row r="335" spans="1:2">
       <c r="A335" t="s">
-        <v>732</v>
+        <v>662</v>
       </c>
       <c r="B335" t="s">
-        <v>733</v>
+        <v>663</v>
       </c>
     </row>
     <row r="336" spans="1:2">
-      <c r="A336" s="5" t="s">
-        <v>734</v>
-      </c>
-      <c r="B336" s="5" t="s">
-        <v>735</v>
+      <c r="A336" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="B336" s="3" t="s">
+        <v>665</v>
       </c>
     </row>
     <row r="337" spans="1:2">
       <c r="A337" t="s">
-        <v>736</v>
+        <v>666</v>
       </c>
       <c r="B337" t="s">
-        <v>737</v>
+        <v>667</v>
       </c>
     </row>
     <row r="338" spans="1:2">
       <c r="A338" t="s">
-        <v>738</v>
+        <v>668</v>
       </c>
       <c r="B338" t="s">
-        <v>739</v>
+        <v>669</v>
       </c>
     </row>
     <row r="339" spans="1:2">
-      <c r="A339" s="5" t="s">
-        <v>740</v>
-      </c>
-      <c r="B339" s="5" t="s">
-        <v>741</v>
+      <c r="A339" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="B339" s="3" t="s">
+        <v>671</v>
       </c>
     </row>
     <row r="340" spans="1:2">
-      <c r="A340" s="7" t="s">
-        <v>742</v>
-      </c>
-      <c r="B340" s="7" t="s">
-        <v>743</v>
+      <c r="A340" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="B340" s="5" t="s">
+        <v>673</v>
       </c>
     </row>
     <row r="341" spans="1:2">
-      <c r="A341" s="7" t="s">
-        <v>744</v>
-      </c>
-      <c r="B341" s="7" t="s">
-        <v>745</v>
+      <c r="A341" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="B341" s="5" t="s">
+        <v>675</v>
       </c>
     </row>
     <row r="342" spans="1:2">
       <c r="A342" t="s">
-        <v>746</v>
+        <v>676</v>
       </c>
       <c r="B342" t="s">
-        <v>747</v>
+        <v>677</v>
       </c>
     </row>
     <row r="343" spans="1:2">
       <c r="A343" t="s">
-        <v>748</v>
+        <v>678</v>
       </c>
       <c r="B343" t="s">
-        <v>749</v>
+        <v>679</v>
       </c>
     </row>
     <row r="344" spans="1:2">
-      <c r="A344" s="5" t="s">
-        <v>750</v>
-      </c>
-      <c r="B344" s="5" t="s">
-        <v>751</v>
+      <c r="A344" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="B344" s="3" t="s">
+        <v>681</v>
       </c>
     </row>
     <row r="345" spans="1:2">
       <c r="A345" t="s">
-        <v>752</v>
+        <v>682</v>
       </c>
       <c r="B345" t="s">
-        <v>753</v>
+        <v>683</v>
       </c>
     </row>
     <row r="346" spans="1:2">
       <c r="A346" t="s">
-        <v>754</v>
+        <v>684</v>
       </c>
       <c r="B346" t="s">
-        <v>755</v>
+        <v>685</v>
       </c>
     </row>
     <row r="347" spans="1:2">
       <c r="A347" t="s">
-        <v>756</v>
+        <v>686</v>
       </c>
       <c r="B347" t="s">
-        <v>757</v>
+        <v>687</v>
       </c>
     </row>
     <row r="348" spans="1:2">
-      <c r="A348" s="7" t="s">
-        <v>758</v>
-      </c>
-      <c r="B348" s="7" t="s">
-        <v>759</v>
+      <c r="A348" s="5" t="s">
+        <v>688</v>
+      </c>
+      <c r="B348" s="5" t="s">
+        <v>689</v>
       </c>
     </row>
     <row r="349" spans="1:2">
-      <c r="A349" s="7" t="s">
-        <v>760</v>
-      </c>
-      <c r="B349" s="7" t="s">
-        <v>761</v>
+      <c r="A349" s="5" t="s">
+        <v>690</v>
+      </c>
+      <c r="B349" s="5" t="s">
+        <v>691</v>
       </c>
     </row>
     <row r="350" spans="1:2">
-      <c r="A350" s="5" t="s">
-        <v>762</v>
-      </c>
-      <c r="B350" s="5" t="s">
-        <v>763</v>
+      <c r="A350" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="B350" s="3" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="351" spans="1:2">
-      <c r="A351" s="5" t="s">
-        <v>764</v>
-      </c>
-      <c r="B351" s="5" t="s">
-        <v>765</v>
+      <c r="A351" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="B351" s="3" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="352" spans="1:2">
       <c r="A352" t="s">
-        <v>766</v>
+        <v>696</v>
       </c>
       <c r="B352" t="s">
-        <v>767</v>
+        <v>697</v>
       </c>
     </row>
     <row r="353" spans="1:2">
-      <c r="A353" s="5" t="s">
-        <v>768</v>
-      </c>
-      <c r="B353" s="5" t="s">
-        <v>769</v>
+      <c r="A353" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="B353" s="3" t="s">
+        <v>699</v>
       </c>
     </row>
     <row r="354" spans="1:2">
-      <c r="A354" s="5" t="s">
-        <v>770</v>
-      </c>
-      <c r="B354" s="5" t="s">
-        <v>771</v>
+      <c r="A354" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="B354" s="3" t="s">
+        <v>701</v>
       </c>
     </row>
     <row r="355" spans="1:2">
-      <c r="A355" s="7" t="s">
-        <v>772</v>
-      </c>
-      <c r="B355" s="7" t="s">
-        <v>773</v>
+      <c r="A355" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="B355" s="5" t="s">
+        <v>703</v>
       </c>
     </row>
     <row r="356" spans="1:2">
-      <c r="A356" s="5" t="s">
-        <v>774</v>
-      </c>
-      <c r="B356" s="5" t="s">
-        <v>775</v>
+      <c r="A356" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="B356" s="3" t="s">
+        <v>705</v>
       </c>
     </row>
     <row r="357" spans="1:2">
       <c r="A357" t="s">
-        <v>776</v>
+        <v>706</v>
       </c>
       <c r="B357" t="s">
-        <v>777</v>
+        <v>707</v>
       </c>
     </row>
     <row r="358" spans="1:2">
-      <c r="A358" s="5" t="s">
-        <v>778</v>
-      </c>
-      <c r="B358" s="5" t="s">
-        <v>779</v>
+      <c r="A358" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="B358" s="3" t="s">
+        <v>709</v>
       </c>
     </row>
     <row r="359" spans="1:2">
       <c r="A359" t="s">
-        <v>780</v>
+        <v>710</v>
       </c>
       <c r="B359" t="s">
-        <v>781</v>
+        <v>711</v>
       </c>
     </row>
     <row r="360" spans="1:2">
       <c r="A360" t="s">
-        <v>782</v>
+        <v>712</v>
       </c>
       <c r="B360" t="s">
-        <v>783</v>
+        <v>713</v>
       </c>
     </row>
     <row r="361" spans="1:2">
-      <c r="A361" s="5" t="s">
-        <v>784</v>
-      </c>
-      <c r="B361" s="5" t="s">
-        <v>785</v>
+      <c r="A361" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="B361" s="3" t="s">
+        <v>715</v>
       </c>
     </row>
     <row r="362" spans="1:2">
-      <c r="A362" s="5" t="s">
-        <v>786</v>
-      </c>
-      <c r="B362" s="5" t="s">
-        <v>787</v>
+      <c r="A362" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="B362" s="3" t="s">
+        <v>717</v>
       </c>
     </row>
     <row r="363" spans="1:2">
       <c r="A363" t="s">
-        <v>788</v>
+        <v>718</v>
       </c>
       <c r="B363" t="s">
-        <v>789</v>
+        <v>719</v>
       </c>
     </row>
     <row r="364" spans="1:2">
       <c r="A364" t="s">
-        <v>790</v>
+        <v>720</v>
       </c>
       <c r="B364" t="s">
-        <v>791</v>
+        <v>721</v>
       </c>
     </row>
     <row r="365" spans="1:2">
-      <c r="A365" s="5" t="s">
-        <v>792</v>
-      </c>
-      <c r="B365" s="5" t="s">
-        <v>793</v>
+      <c r="A365" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="B365" s="3" t="s">
+        <v>723</v>
       </c>
     </row>
     <row r="366" spans="1:2">
-      <c r="A366" s="7" t="s">
-        <v>794</v>
-      </c>
-      <c r="B366" s="7" t="s">
-        <v>795</v>
+      <c r="A366" s="5" t="s">
+        <v>724</v>
+      </c>
+      <c r="B366" s="5" t="s">
+        <v>725</v>
       </c>
     </row>
     <row r="367" spans="1:2">
       <c r="A367" t="s">
-        <v>796</v>
+        <v>726</v>
       </c>
       <c r="B367" t="s">
-        <v>797</v>
+        <v>727</v>
       </c>
     </row>
     <row r="368" spans="1:2">
       <c r="A368" t="s">
-        <v>798</v>
+        <v>728</v>
       </c>
       <c r="B368" t="s">
-        <v>799</v>
+        <v>729</v>
       </c>
     </row>
     <row r="369" spans="1:2">
       <c r="A369" t="s">
-        <v>800</v>
+        <v>730</v>
       </c>
       <c r="B369" t="s">
-        <v>801</v>
+        <v>731</v>
       </c>
     </row>
     <row r="370" spans="1:2">
-      <c r="A370" s="5" t="s">
-        <v>802</v>
-      </c>
-      <c r="B370" s="5" t="s">
-        <v>803</v>
+      <c r="A370" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="B370" s="3" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="371" spans="1:2">
-      <c r="A371" s="5" t="s">
-        <v>804</v>
-      </c>
-      <c r="B371" s="5" t="s">
-        <v>805</v>
+      <c r="A371" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="B371" s="3" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="372" spans="1:2">
       <c r="A372" t="s">
-        <v>806</v>
+        <v>736</v>
       </c>
       <c r="B372" t="s">
-        <v>807</v>
+        <v>737</v>
       </c>
     </row>
     <row r="373" spans="1:2">
       <c r="A373" t="s">
-        <v>808</v>
+        <v>738</v>
       </c>
       <c r="B373" t="s">
-        <v>809</v>
+        <v>739</v>
       </c>
     </row>
     <row r="374" spans="1:2">
-      <c r="A374" s="5" t="s">
-        <v>810</v>
-      </c>
-      <c r="B374" s="5" t="s">
-        <v>811</v>
+      <c r="A374" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="B374" s="3" t="s">
+        <v>741</v>
       </c>
     </row>
     <row r="375" spans="1:2">
-      <c r="A375" s="5" t="s">
-        <v>812</v>
-      </c>
-      <c r="B375" s="5" t="s">
-        <v>813</v>
+      <c r="A375" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="B375" s="3" t="s">
+        <v>743</v>
       </c>
     </row>
     <row r="376" spans="1:2">
-      <c r="A376" s="5" t="s">
-        <v>814</v>
-      </c>
-      <c r="B376" s="5" t="s">
-        <v>815</v>
+      <c r="A376" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="B376" s="3" t="s">
+        <v>745</v>
       </c>
     </row>
     <row r="377" spans="1:2">
       <c r="A377" t="s">
-        <v>816</v>
+        <v>746</v>
       </c>
       <c r="B377" t="s">
-        <v>817</v>
+        <v>747</v>
       </c>
     </row>
     <row r="378" spans="1:2">
       <c r="A378" t="s">
-        <v>818</v>
+        <v>748</v>
       </c>
       <c r="B378" t="s">
-        <v>819</v>
+        <v>749</v>
       </c>
     </row>
     <row r="379" spans="1:2">
-      <c r="A379" s="5" t="s">
-        <v>820</v>
-      </c>
-      <c r="B379" s="5" t="s">
-        <v>821</v>
+      <c r="A379" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="B379" s="3" t="s">
+        <v>751</v>
       </c>
     </row>
     <row r="380" spans="1:2">
       <c r="A380" t="s">
-        <v>822</v>
+        <v>752</v>
       </c>
       <c r="B380" t="s">
-        <v>823</v>
+        <v>753</v>
       </c>
     </row>
     <row r="381" spans="1:2">
       <c r="A381" t="s">
-        <v>824</v>
+        <v>754</v>
       </c>
       <c r="B381" t="s">
-        <v>825</v>
+        <v>755</v>
       </c>
     </row>
     <row r="382" spans="1:2">
-      <c r="A382" s="5" t="s">
-        <v>826</v>
-      </c>
-      <c r="B382" s="5" t="s">
-        <v>827</v>
+      <c r="A382" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="B382" s="3" t="s">
+        <v>757</v>
       </c>
     </row>
     <row r="383" spans="1:2">
       <c r="A383" t="s">
-        <v>828</v>
+        <v>758</v>
       </c>
       <c r="B383" t="s">
-        <v>829</v>
+        <v>759</v>
       </c>
     </row>
     <row r="384" spans="1:2">
       <c r="A384" t="s">
-        <v>830</v>
+        <v>760</v>
       </c>
       <c r="B384" t="s">
-        <v>831</v>
+        <v>761</v>
       </c>
     </row>
     <row r="385" spans="1:2">
       <c r="A385" t="s">
-        <v>832</v>
+        <v>762</v>
       </c>
       <c r="B385" t="s">
-        <v>833</v>
+        <v>763</v>
       </c>
     </row>
     <row r="386" spans="1:2">
-      <c r="A386" s="5"/>
-      <c r="B386" s="5"/>
+      <c r="A386" s="3"/>
+      <c r="B386" s="3"/>
     </row>
     <row r="387" spans="1:2">
-      <c r="A387" s="5"/>
-      <c r="B387" s="5"/>
+      <c r="A387" s="3"/>
+      <c r="B387" s="3"/>
     </row>
     <row r="388" spans="1:2">
       <c r="A388"/>
@@ -6548,82 +5946,82 @@
     </row>
     <row r="389" spans="1:2">
       <c r="A389" t="s">
-        <v>834</v>
+        <v>764</v>
       </c>
       <c r="B389" t="s">
-        <v>835</v>
+        <v>765</v>
       </c>
     </row>
     <row r="390" spans="1:2">
       <c r="A390" t="s">
-        <v>333</v>
+        <v>269</v>
       </c>
       <c r="B390" t="s">
-        <v>334</v>
+        <v>270</v>
       </c>
     </row>
     <row r="391" spans="1:2">
-      <c r="A391" s="5" t="s">
-        <v>836</v>
-      </c>
-      <c r="B391" s="5" t="s">
-        <v>837</v>
+      <c r="A391" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="B391" s="3" t="s">
+        <v>767</v>
       </c>
     </row>
     <row r="392" spans="1:2">
-      <c r="A392" s="5"/>
-      <c r="B392" s="5"/>
+      <c r="A392" s="3"/>
+      <c r="B392" s="3"/>
     </row>
     <row r="393" spans="1:2">
       <c r="A393"/>
       <c r="B393"/>
     </row>
     <row r="394" spans="1:2">
-      <c r="A394" s="5"/>
-      <c r="B394" s="5"/>
+      <c r="A394" s="3"/>
+      <c r="B394" s="3"/>
     </row>
     <row r="396" spans="1:2">
       <c r="A396"/>
       <c r="B396"/>
     </row>
     <row r="397" spans="1:2">
-      <c r="A397" s="5" t="s">
-        <v>838</v>
-      </c>
-      <c r="B397" s="5" t="s">
-        <v>839</v>
+      <c r="A397" s="3" t="s">
+        <v>768</v>
+      </c>
+      <c r="B397" s="3" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="398" spans="1:2">
-      <c r="A398" s="5"/>
-      <c r="B398" s="5"/>
+      <c r="A398" s="3"/>
+      <c r="B398" s="3"/>
     </row>
     <row r="399" spans="1:2">
-      <c r="A399" s="5" t="s">
-        <v>840</v>
-      </c>
-      <c r="B399" s="5" t="s">
-        <v>841</v>
+      <c r="A399" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="B399" s="3" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="400" spans="1:2">
       <c r="A400" t="s">
-        <v>842</v>
+        <v>772</v>
       </c>
       <c r="B400" t="s">
-        <v>843</v>
+        <v>773</v>
       </c>
     </row>
     <row r="401" spans="1:2">
-      <c r="A401" s="5"/>
-      <c r="B401" s="5"/>
+      <c r="A401" s="3"/>
+      <c r="B401" s="3"/>
     </row>
     <row r="402" spans="1:2">
       <c r="A402" t="s">
-        <v>844</v>
+        <v>774</v>
       </c>
       <c r="B402" t="s">
-        <v>845</v>
+        <v>775</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -6631,16 +6029,16 @@
       <c r="B403"/>
     </row>
     <row r="404" spans="1:2">
-      <c r="A404" s="5"/>
-      <c r="B404" s="5"/>
+      <c r="A404" s="3"/>
+      <c r="B404" s="3"/>
     </row>
     <row r="405" spans="1:2">
       <c r="A405"/>
       <c r="B405"/>
     </row>
     <row r="406" spans="1:2">
-      <c r="A406" s="12"/>
-      <c r="B406" s="12"/>
+      <c r="A406" s="10"/>
+      <c r="B406" s="10"/>
     </row>
     <row r="407" spans="1:2">
       <c r="A407"/>
@@ -6651,8 +6049,8 @@
       <c r="B408"/>
     </row>
     <row r="409" spans="1:2">
-      <c r="A409" s="5"/>
-      <c r="B409" s="5"/>
+      <c r="A409" s="3"/>
+      <c r="B409" s="3"/>
     </row>
     <row r="410" spans="1:2">
       <c r="A410"/>
@@ -6671,28 +6069,28 @@
       <c r="B413"/>
     </row>
     <row r="414" spans="1:2">
-      <c r="A414" s="5"/>
-      <c r="B414" s="5"/>
+      <c r="A414" s="3"/>
+      <c r="B414" s="3"/>
     </row>
     <row r="415" spans="1:2">
       <c r="A415" t="s">
-        <v>846</v>
+        <v>776</v>
       </c>
       <c r="B415" t="s">
-        <v>847</v>
+        <v>777</v>
       </c>
     </row>
     <row r="416" spans="1:2">
-      <c r="A416" s="5" t="s">
-        <v>848</v>
-      </c>
-      <c r="B416" s="5" t="s">
-        <v>849</v>
+      <c r="A416" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="B416" s="3" t="s">
+        <v>779</v>
       </c>
     </row>
     <row r="417" spans="1:2">
-      <c r="A417" s="13"/>
-      <c r="B417" s="13"/>
+      <c r="A417" s="11"/>
+      <c r="B417" s="11"/>
     </row>
     <row r="418" spans="1:2">
       <c r="A418"/>
@@ -6708,42 +6106,42 @@
     </row>
     <row r="421" spans="1:2">
       <c r="A421" t="s">
-        <v>850</v>
+        <v>780</v>
       </c>
       <c r="B421" t="s">
-        <v>851</v>
+        <v>781</v>
       </c>
     </row>
     <row r="422" spans="1:2">
-      <c r="A422" s="14"/>
-      <c r="B422" s="14"/>
+      <c r="A422" s="12"/>
+      <c r="B422" s="12"/>
     </row>
     <row r="423" spans="1:2">
-      <c r="A423" s="12"/>
-      <c r="B423" s="12"/>
+      <c r="A423" s="10"/>
+      <c r="B423" s="10"/>
     </row>
     <row r="424" spans="1:2">
-      <c r="A424" s="5"/>
-      <c r="B424" s="5"/>
+      <c r="A424" s="3"/>
+      <c r="B424" s="3"/>
     </row>
     <row r="425" spans="1:2">
       <c r="A425"/>
       <c r="B425"/>
     </row>
     <row r="426" spans="1:2">
-      <c r="A426" s="5"/>
-      <c r="B426" s="5"/>
+      <c r="A426" s="3"/>
+      <c r="B426" s="3"/>
     </row>
     <row r="427" spans="1:2">
       <c r="A427"/>
       <c r="B427"/>
     </row>
     <row r="428" spans="1:2">
-      <c r="A428" s="5" t="s">
-        <v>853</v>
-      </c>
-      <c r="B428" s="5" t="s">
-        <v>854</v>
+      <c r="A428" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="B428" s="3" t="s">
+        <v>783</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -6755,8 +6153,8 @@
       <c r="B430"/>
     </row>
     <row r="431" spans="1:2">
-      <c r="A431" s="5"/>
-      <c r="B431" s="5"/>
+      <c r="A431" s="3"/>
+      <c r="B431" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6764,14 +6162,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C04419A4-ABD5-463C-A44D-E18099D3F2F0}">
   <dimension ref="A2"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/исправления внести/слова3.xlsx
+++ b/исправления внести/слова3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\исправления внести\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830D2B2A-E9E2-4FE0-98E1-31AFDCDB4708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9E2965-3EE7-4675-A6B7-6EC9A0925047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="24768" windowHeight="12432" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
   </bookViews>
   <sheets>
     <sheet name="cоставные" sheetId="2" r:id="rId1"/>
@@ -32,22 +32,19 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="572">
   <si>
     <t>биологический структурализм</t>
   </si>
   <si>
-    <t>прямых излучения</t>
-  </si>
-  <si>
-    <t>прямых излучений</t>
-  </si>
-  <si>
     <t>кто в этом случая</t>
   </si>
   <si>
@@ -84,12 +81,6 @@
     <t>контактантов</t>
   </si>
   <si>
-    <t>тем самым занижает свой возможности разума</t>
-  </si>
-  <si>
-    <t>тем самым занижает свои возможности разума</t>
-  </si>
-  <si>
     <t>богословно-управленческий заведение эту толкование</t>
   </si>
   <si>
@@ -102,48 +93,18 @@
     <t>последователи этой обособленные закрытые вероучения</t>
   </si>
   <si>
-    <t xml:space="preserve"> Чтобы произошла воплощение вашей мыслеобраза</t>
-  </si>
-  <si>
-    <t>Чтобы произошло воплощение вашего мыслеобраза</t>
-  </si>
-  <si>
-    <t>это основа высшей колдовства</t>
-  </si>
-  <si>
-    <t>это основа высшего колдовства</t>
-  </si>
-  <si>
     <t>общего научного савокупности миропонимания</t>
   </si>
   <si>
     <t>общей научной савокупности миропонимания</t>
   </si>
   <si>
-    <t>это папка можно получить многомерную чертеж-рисунок</t>
-  </si>
-  <si>
-    <t>этой папкой можно получить многомерный чертеж-рисунок</t>
-  </si>
-  <si>
-    <t>этот последствие был великолепноопытно доказан академиком</t>
-  </si>
-  <si>
-    <t>это последствие было  великолепноопытно доказано  академиком</t>
-  </si>
-  <si>
     <t>важное положение существование большой скрытого вещества</t>
   </si>
   <si>
     <t>важное положение существование большого скрытого вещества</t>
   </si>
   <si>
-    <t>смертельный для любой общества</t>
-  </si>
-  <si>
-    <t>смертельный для любого общества</t>
-  </si>
-  <si>
     <t>запасенный жизненный щаряд вращение скрученного</t>
   </si>
   <si>
@@ -186,12 +147,6 @@
     <t>Вода является двухмерным отображением рычага</t>
   </si>
   <si>
-    <t>хранит внушительный количество сведениям</t>
-  </si>
-  <si>
-    <t>хранит внушительное количество сведенй</t>
-  </si>
-  <si>
     <t>наступают связующие случая</t>
   </si>
   <si>
@@ -216,12 +171,6 @@
     <t>как "считываются" сведения</t>
   </si>
   <si>
-    <t>тонкие руки и ножи</t>
-  </si>
-  <si>
-    <t>тонкие руки и ноги</t>
-  </si>
-  <si>
     <t>очередная обьединение общества</t>
   </si>
   <si>
@@ -240,36 +189,18 @@
     <t>последствие известно давно</t>
   </si>
   <si>
-    <t>А "марсианский метеорит" полностью добил эту учение</t>
-  </si>
-  <si>
-    <t>А "марсианский метеорит" полностью добил это учение</t>
-  </si>
-  <si>
     <t>На первый взгляд жуткий истребление народа</t>
   </si>
   <si>
     <t>На первый взгляд жуткое истребление народа</t>
   </si>
   <si>
-    <t>способности к парения в воздухе</t>
-  </si>
-  <si>
-    <t>способности к парению в воздухе</t>
-  </si>
-  <si>
     <t>по 10 сложилась случай воплощения</t>
   </si>
   <si>
     <t>по 10 сложился случай воплощения</t>
   </si>
   <si>
-    <t>Случай коренным образом изменился при рассмотрении</t>
-  </si>
-  <si>
-    <t>Случай коренным образом изменилась при рассмотрении</t>
-  </si>
-  <si>
     <t>один из парламентариев в беседа</t>
   </si>
   <si>
@@ -282,12 +213,6 @@
     <t>после любого даже незначительного увечья</t>
   </si>
   <si>
-    <t>удалось заразить минингитоподобным заразой</t>
-  </si>
-  <si>
-    <t>удалось заразить минингитоподобной заразой</t>
-  </si>
-  <si>
     <t>внедрение энергоинформационного зараза</t>
   </si>
   <si>
@@ -306,12 +231,6 @@
     <t>паталогия в развитии землян</t>
   </si>
   <si>
-    <t>протекающий по завитка</t>
-  </si>
-  <si>
-    <t>протекающий по завиткам</t>
-  </si>
-  <si>
     <t>наше небесное тело было превращено в некое жертвенное посевное поле</t>
   </si>
   <si>
@@ -336,36 +255,12 @@
     <t>об энергоинформационном устройстве человека</t>
   </si>
   <si>
-    <t>При этом образуется количественная устройство напоминающая</t>
-  </si>
-  <si>
-    <t>При этом образуется количественное  устройство напоминаящее</t>
-  </si>
-  <si>
     <t>наша существующая живая особь</t>
   </si>
   <si>
     <t>наш существующий живая особь</t>
   </si>
   <si>
-    <t>точную самоповтор исходного живой особи</t>
-  </si>
-  <si>
-    <t>точный самоповтор исходной живой особи</t>
-  </si>
-  <si>
-    <t>происходит  разрушение внутренней устройства</t>
-  </si>
-  <si>
-    <t>происходит  разрушение внутреннего устройства</t>
-  </si>
-  <si>
-    <t>тайноведов прошлого и настоящего позволил сделать</t>
-  </si>
-  <si>
-    <t>тайноведов прошлого и настоящего позволило сделать</t>
-  </si>
-  <si>
     <t>ожидает весьма неприятная случай</t>
   </si>
   <si>
@@ -402,36 +297,18 @@
     <t>за последнее время земным обществом</t>
   </si>
   <si>
-    <t>такой правило работы просто вынуждал</t>
-  </si>
-  <si>
-    <t>такой правило работы просто вынуждало</t>
-  </si>
-  <si>
     <t>есть какая то щелчка, действующая на погибель</t>
   </si>
   <si>
     <t>есть какой то щелчок, действующий на погибель</t>
   </si>
   <si>
-    <t>свою отведенную значение</t>
-  </si>
-  <si>
-    <t>свое отведенное значение</t>
-  </si>
-  <si>
     <t>нельзя было дать российскому народу</t>
   </si>
   <si>
     <t>нельзя было дать российскому народности</t>
   </si>
   <si>
-    <t>символом древнейшей испанской колдовства</t>
-  </si>
-  <si>
-    <t>символом древнейшего испанского колдовства</t>
-  </si>
-  <si>
     <t>ПечатьСША в своей обозначении</t>
   </si>
   <si>
@@ -528,12 +405,6 @@
     <t>к снижению  энергетического возможности человека</t>
   </si>
   <si>
-    <t>хранитель тайноведения или тайный семья</t>
-  </si>
-  <si>
-    <t>хранитель тайноведения или тайная семья</t>
-  </si>
-  <si>
     <t>злая небесное тело Сатурн</t>
   </si>
   <si>
@@ -546,12 +417,6 @@
     <t>вспомните вот такую проверочный случай</t>
   </si>
   <si>
-    <t>так бы увидел эту изображению ясновидящий</t>
-  </si>
-  <si>
-    <t>так бы увидел это изображение ясновидящий</t>
-  </si>
-  <si>
     <t>замысел жертвы на восковую образу</t>
   </si>
   <si>
@@ -564,18 +429,6 @@
     <t>рядом количественный скачок</t>
   </si>
   <si>
-    <t>Эти случая воспроизводятся</t>
-  </si>
-  <si>
-    <t>Эти случаи воспроизводятся</t>
-  </si>
-  <si>
-    <t>проверочная случай в автобусе произошла</t>
-  </si>
-  <si>
-    <t>проверочный случай в автобусе произошел</t>
-  </si>
-  <si>
     <t>на восковую образу</t>
   </si>
   <si>
@@ -612,12 +465,6 @@
     <t>Когда сложенный заряд излучения</t>
   </si>
   <si>
-    <t>При показания этого движения рук</t>
-  </si>
-  <si>
-    <t>При показании этого движения рук</t>
-  </si>
-  <si>
     <t>В науки о нло давно известно</t>
   </si>
   <si>
@@ -642,12 +489,6 @@
     <t>Для этого нехитрого действия</t>
   </si>
   <si>
-    <t>применяются в разрушающего колдовства</t>
-  </si>
-  <si>
-    <t>применяются в разрушающем колдовстве</t>
-  </si>
-  <si>
     <t>будем от эниологического учения переходить к применению</t>
   </si>
   <si>
@@ -696,12 +537,6 @@
     <t>объединяются в семью, не в том особенность</t>
   </si>
   <si>
-    <t>С этого особенности в Несущих сведения Полях</t>
-  </si>
-  <si>
-    <t>С этой особенности в Несущих сведениях  Полях</t>
-  </si>
-  <si>
     <t>В тот особенность когда Николай</t>
   </si>
   <si>
@@ -714,48 +549,24 @@
     <t>в ИП остается ваше местоположение нападения</t>
   </si>
   <si>
-    <t>Это было ответным предложением мощнейшей волшебной семьи</t>
-  </si>
-  <si>
-    <t>Это была ответная предложения мощнейшая волшебного семьи</t>
-  </si>
-  <si>
     <t>Поэтому индийский колдовской семья был вынужден</t>
   </si>
   <si>
     <t>Поэтому индийская колдовская семья была вынуждена</t>
   </si>
   <si>
-    <t>при этом прихватить ваш возможность</t>
-  </si>
-  <si>
-    <t>при этом прихватить вашу возможность</t>
-  </si>
-  <si>
     <t>За какую приказ вы болеете</t>
   </si>
   <si>
     <t>За какой приказ вы болеете</t>
   </si>
   <si>
-    <t>строго определенный местоположение в Несущих</t>
-  </si>
-  <si>
-    <t>строго определенное местоположение в Несущих</t>
-  </si>
-  <si>
     <t>перехода к рыночной рапределении</t>
   </si>
   <si>
     <t>перехода к рыночному рапределению</t>
   </si>
   <si>
-    <t>существует и более тонкий особенность правила</t>
-  </si>
-  <si>
-    <t>существует и более тонкая особенность правил</t>
-  </si>
-  <si>
     <t>касается не только определенной эниологической применения</t>
   </si>
   <si>
@@ -774,24 +585,6 @@
     <t>занятии был раскрыт какой-то вопрос</t>
   </si>
   <si>
-    <t>приступить к следующей вопросе</t>
-  </si>
-  <si>
-    <t>приступить к следующему вопросу</t>
-  </si>
-  <si>
-    <t>Следующий проверочный случай</t>
-  </si>
-  <si>
-    <t>Следующая проверочная случай</t>
-  </si>
-  <si>
-    <t>статья на нужную вопрос</t>
-  </si>
-  <si>
-    <t>статья на нужный вопрос</t>
-  </si>
-  <si>
     <t>необязательно в той образе</t>
   </si>
   <si>
@@ -804,12 +597,6 @@
     <t>пока этот глупейший случай существует</t>
   </si>
   <si>
-    <t>является служба в вооруженные силы</t>
-  </si>
-  <si>
-    <t>является служба в вооруженных силах</t>
-  </si>
-  <si>
     <t>этапе энергоинформационой изменения</t>
   </si>
   <si>
@@ -864,12 +651,6 @@
     <t>в основном множестве школ</t>
   </si>
   <si>
-    <t>тот колдовской совместное сознание</t>
-  </si>
-  <si>
-    <t>то колдовское совместное сознание</t>
-  </si>
-  <si>
     <t>вернуть изъятый возможность</t>
   </si>
   <si>
@@ -882,12 +663,6 @@
     <t>в итоге   проводимого изменения</t>
   </si>
   <si>
-    <t>такую изображению</t>
-  </si>
-  <si>
-    <t>такое изображение</t>
-  </si>
-  <si>
     <t>выделяется "чистая заряд"которая идет</t>
   </si>
   <si>
@@ -912,24 +687,6 @@
     <t>в полном налаживании энергоинформационного обмена</t>
   </si>
   <si>
-    <t>совершено разная ответ</t>
-  </si>
-  <si>
-    <t>совершено разный ответ</t>
-  </si>
-  <si>
-    <t>язык общения по свой устройстве</t>
-  </si>
-  <si>
-    <t>язык общения по своему устройству</t>
-  </si>
-  <si>
-    <t>при помощи коротых общается данный народность</t>
-  </si>
-  <si>
-    <t>при помощи коротых общается данная народность</t>
-  </si>
-  <si>
     <t>значения мата в развития росийского народности</t>
   </si>
   <si>
@@ -942,12 +699,6 @@
     <t>верят исконному целительству</t>
   </si>
   <si>
-    <t>церковная колдовство позволяет</t>
-  </si>
-  <si>
-    <t>церковное колдовство позволяет</t>
-  </si>
-  <si>
     <t>оставивших в ИП  свой местопожение  проклятий</t>
   </si>
   <si>
@@ -984,78 +735,30 @@
     <t>высвобождение неиспользованной возможности</t>
   </si>
   <si>
-    <t>Этой  вопросе посвящен раздел</t>
-  </si>
-  <si>
-    <t>Этому  вопросу посвящен раздел</t>
-  </si>
-  <si>
-    <t>Причем этой вопросе</t>
-  </si>
-  <si>
-    <t>Причем этому вопросу</t>
-  </si>
-  <si>
     <t>не было посвящено ни одной обнародования</t>
   </si>
   <si>
     <t>не было посвящено ни одного обнародования</t>
   </si>
   <si>
-    <t>у одной больные женщины просматривался сильнейший</t>
-  </si>
-  <si>
-    <t>у одной больной женщины просматривался сильнейшее</t>
-  </si>
-  <si>
     <t>В армянской колдовства для снятия порчи</t>
   </si>
   <si>
     <t>В армянском колдовстве для снятия порчи</t>
   </si>
   <si>
-    <t>человек попадает в важнейшую случай</t>
-  </si>
-  <si>
-    <t>человек попадает в важный случай</t>
-  </si>
-  <si>
     <t>в итоге крупной увечья</t>
   </si>
   <si>
     <t>в итоге крупных увечий</t>
   </si>
   <si>
-    <t>У больные женщины при эникоррекции</t>
-  </si>
-  <si>
-    <t>У больной женщины при эникоррекции</t>
-  </si>
-  <si>
     <t>был обнаружен сильнейший перенапряжение</t>
   </si>
   <si>
     <t>был обнаружено сильнейшее перенапряжение</t>
   </si>
   <si>
-    <t>связанный с похоронами</t>
-  </si>
-  <si>
-    <t>связанное с похоронами</t>
-  </si>
-  <si>
-    <t>сильнейшей черепно-мозговой  увечья</t>
-  </si>
-  <si>
-    <t>сильнейшего черепно-мозгового  увечья</t>
-  </si>
-  <si>
-    <t>Этой вопросе посвящено</t>
-  </si>
-  <si>
-    <t>Этому вопросу посвящено</t>
-  </si>
-  <si>
     <t>рассмотреть сам особенность</t>
   </si>
   <si>
@@ -1110,30 +813,12 @@
     <t>дали очень увлекательный подсчет</t>
   </si>
   <si>
-    <t>Скурпулезный оценка нарушений этапов</t>
-  </si>
-  <si>
-    <t>Скурпулезная оценка нарушений этапов</t>
-  </si>
-  <si>
     <t>привела его на тот же землеописаной сечение</t>
   </si>
   <si>
     <t>привела его на то же землеописаное сечение</t>
   </si>
   <si>
-    <t>хорошо предусмотрена эта естественная случай</t>
-  </si>
-  <si>
-    <t>хорошо предусмотрен этот естественный случай</t>
-  </si>
-  <si>
-    <t>случай требует скурпулезного оценки</t>
-  </si>
-  <si>
-    <t>случай требует скурпулезной оценки</t>
-  </si>
-  <si>
     <t>не запретила основной множесте людей</t>
   </si>
   <si>
@@ -1230,30 +915,12 @@
     <t>забраться на главную высшую точку</t>
   </si>
   <si>
-    <t>своему семье безбедное существование</t>
-  </si>
-  <si>
-    <t>своей семье безбедное существование</t>
-  </si>
-  <si>
     <t>в итоге всей этого случая</t>
   </si>
   <si>
     <t>в итоге всего этого случая</t>
   </si>
   <si>
-    <t>тогда весь представление</t>
-  </si>
-  <si>
-    <t>тогда все представление</t>
-  </si>
-  <si>
-    <t>этот скользкий особенность из Библии:</t>
-  </si>
-  <si>
-    <t>эту скользкую особенность из Библии:</t>
-  </si>
-  <si>
     <t>на всю небесному телу приоткрывается «личико творца-благодетеля».</t>
   </si>
   <si>
@@ -1278,18 +945,6 @@
     <t>особенность «сотворения» проводиась</t>
   </si>
   <si>
-    <t>Самая обычный связующая случай,</t>
-  </si>
-  <si>
-    <t>Самая обычный связующий случай,</t>
-  </si>
-  <si>
-    <t>согласно церковной трактования,</t>
-  </si>
-  <si>
-    <t>согласно церковному трактованию,</t>
-  </si>
-  <si>
     <t>Исходя из церковной трактованиям</t>
   </si>
   <si>
@@ -1350,12 +1005,6 @@
     <t>на все небесное тело приоткрывается «</t>
   </si>
   <si>
-    <t>смерти выделяется весь неиспользованный возможность</t>
-  </si>
-  <si>
-    <t>смерти выделяется вся неиспользованная возможность</t>
-  </si>
-  <si>
     <t>переосмысливая каждую выражение.</t>
   </si>
   <si>
@@ -1380,12 +1029,6 @@
     <t>в самую последнюю, важнейшую особенность</t>
   </si>
   <si>
-    <t>преодолеть энергоинформационный разногласие.</t>
-  </si>
-  <si>
-    <t>преодолеть энергоинформационное разногласие.</t>
-  </si>
-  <si>
     <t>прекрасной ни была расчётный прообраз</t>
   </si>
   <si>
@@ -1398,30 +1041,12 @@
     <t>дать послойное изображение любого наземного</t>
   </si>
   <si>
-    <t>снимке проявлялся полностью целый страница</t>
-  </si>
-  <si>
-    <t>снимке проявлялась полностью целая страница</t>
-  </si>
-  <si>
-    <t>Сведения сохраняется и после прохождения</t>
-  </si>
-  <si>
-    <t>Сведения сохраняются и после прохождения</t>
-  </si>
-  <si>
     <t>в мой энергоинформационный хранилище.</t>
   </si>
   <si>
     <t>в мое энергоинформационное хранилище.</t>
   </si>
   <si>
-    <t xml:space="preserve"> проводниками основной воззрения</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> проводниками основного воззрения</t>
-  </si>
-  <si>
     <t>Вода после энергоинформационной устранения</t>
   </si>
   <si>
@@ -1494,12 +1119,6 @@
     <t>запись всех сведений о человеке,</t>
   </si>
   <si>
-    <t>содержит полную личную сведения о человеке</t>
-  </si>
-  <si>
-    <t>содержит полные личные сведения о человеке</t>
-  </si>
-  <si>
     <t xml:space="preserve">чувственный обстановка, </t>
   </si>
   <si>
@@ -1518,24 +1137,12 @@
     <t>глупее должна быть объявление</t>
   </si>
   <si>
-    <t>При этом сам обстоятельство просмотра </t>
-  </si>
-  <si>
-    <t>При этом само обстоятельство просмотра </t>
-  </si>
-  <si>
     <t>добровольный правило</t>
   </si>
   <si>
     <t>добровольное правило</t>
   </si>
   <si>
-    <t>Этот случай в последние годы развилась</t>
-  </si>
-  <si>
-    <t>Этот случай в последние годы развилс я</t>
-  </si>
-  <si>
     <t>энергоинформационного возможности!</t>
   </si>
   <si>
@@ -1566,24 +1173,12 @@
     <t>в мою энергоинформационную возможность</t>
   </si>
   <si>
-    <t>удостоверять само обстоятельство, </t>
-  </si>
-  <si>
-    <t>удостоверять сам обстоятельство, </t>
-  </si>
-  <si>
     <t>Ведь это проверочная случай, </t>
   </si>
   <si>
     <t>Ведь это проверочный случай, </t>
   </si>
   <si>
-    <t>применяется при устранения отрицательных</t>
-  </si>
-  <si>
-    <t>применяется при устранении отрицательных</t>
-  </si>
-  <si>
     <t>В более упрощенной образе, </t>
   </si>
   <si>
@@ -1606,12 +1201,6 @@
   </si>
   <si>
     <t>получить вездеприменимую письменность.</t>
-  </si>
-  <si>
-    <t>производить изъятие творческого возможности</t>
-  </si>
-  <si>
-    <t>производить изъятие творческой возможности</t>
   </si>
   <si>
     <r>
@@ -1636,12 +1225,6 @@
     </r>
   </si>
   <si>
-    <t>устраивали еще одно проверка</t>
-  </si>
-  <si>
-    <t>устраивали еще одну проверку</t>
-  </si>
-  <si>
     <t>отрицательный энергоинформационный возможность,</t>
   </si>
   <si>
@@ -1696,12 +1279,6 @@
     <t>барабашки был необходим</t>
   </si>
   <si>
-    <t>Там была полностью обычная уровень тепла!</t>
-  </si>
-  <si>
-    <t>Там был полностью обычный уровень тепла!</t>
-  </si>
-  <si>
     <t>но оказалась работоспособной,</t>
   </si>
   <si>
@@ -1750,12 +1327,6 @@
     <t>городе развивался следующим образом.</t>
   </si>
   <si>
-    <t xml:space="preserve">Эту «отдел», скрытую в подвале спортивного заведения </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Этоь «отдел», скрытый в подвале спортивного заведения </t>
-  </si>
-  <si>
     <t xml:space="preserve">мыслительная матрица начинала воплощать эти запахи </t>
   </si>
   <si>
@@ -1768,30 +1339,12 @@
     <t>быа проведена полнаая оценка</t>
   </si>
   <si>
-    <t xml:space="preserve">уже был набран этот письменность, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">уже была  набрана эта письменность, </t>
-  </si>
-  <si>
-    <t>у власть имущих впал наш Сосредоточение</t>
-  </si>
-  <si>
-    <t>у власть имущих впало наше Сосредоточение</t>
-  </si>
-  <si>
     <t>Подход современной исконного целительства</t>
   </si>
   <si>
     <t>Подход современного исконного целительства</t>
   </si>
   <si>
-    <t>Современная целительство</t>
-  </si>
-  <si>
-    <t>Современное целительство</t>
-  </si>
-  <si>
     <t>непонятных исконной целительстве заболеваний.</t>
   </si>
   <si>
@@ -1846,36 +1399,12 @@
     <t>международным целительским преступным устройством,</t>
   </si>
   <si>
-    <t>торговавшей жертвенными органами</t>
-  </si>
-  <si>
-    <t>торговавшым жертвенными органами</t>
-  </si>
-  <si>
-    <t>так называемый абортный сырьё.</t>
-  </si>
-  <si>
-    <t>так называемое абортное сырьё.</t>
-  </si>
-  <si>
     <t>в предыдущей перерождения</t>
   </si>
   <si>
     <t>в предыдущем перерождении</t>
   </si>
   <si>
-    <t>своих жевательных чутья,</t>
-  </si>
-  <si>
-    <t>своих жевательных чувств</t>
-  </si>
-  <si>
-    <t>Этой вопросе посвящена постоянная</t>
-  </si>
-  <si>
-    <t>Этому вопросу посвящена постоянная</t>
-  </si>
-  <si>
     <t>полная восстановление</t>
   </si>
   <si>
@@ -1888,12 +1417,6 @@
     <t>дистанционное изменение. </t>
   </si>
   <si>
-    <t>что любой связь с</t>
-  </si>
-  <si>
-    <t>что любая связь с</t>
-  </si>
-  <si>
     <t>Общая изображение Установки Внедрения и</t>
   </si>
   <si>
@@ -1948,12 +1471,6 @@
     <t>из временных промежутков лжеразумности</t>
   </si>
   <si>
-    <t>разумной образе существования.</t>
-  </si>
-  <si>
-    <t>разумному образу существования.</t>
-  </si>
-  <si>
     <t>любая образ враждебности</t>
   </si>
   <si>
@@ -2020,12 +1537,6 @@
     <t>за счет жертвенной живой особи человека.</t>
   </si>
   <si>
-    <t>при проведении энергоинформационной изменения,</t>
-  </si>
-  <si>
-    <t>при проведении энергоинформационного изменения,</t>
-  </si>
-  <si>
     <t>дать метастазную образу заболевания. </t>
   </si>
   <si>
@@ -2044,18 +1555,6 @@
     <t>выделится при полном крахе общества</t>
   </si>
   <si>
-    <t>«энергетический» возможность женщины становился меньше,</t>
-  </si>
-  <si>
-    <t>«энергетическая» возможность женщины становилась меньше,</t>
-  </si>
-  <si>
-    <t>проводился общий посещение</t>
-  </si>
-  <si>
-    <t>проводилось общее посещение</t>
-  </si>
-  <si>
     <t>называли эту отдел ученых,</t>
   </si>
   <si>
@@ -2068,12 +1567,6 @@
     <t>взять на оценку жидкость из легких</t>
   </si>
   <si>
-    <t>провели оценка внутрилегочной жидкости,</t>
-  </si>
-  <si>
-    <t>провели оценку внутрилегочной жидкости,</t>
-  </si>
-  <si>
     <t>имени больные женщины, впервые принесшей</t>
   </si>
   <si>
@@ -2092,18 +1585,6 @@
     <t>действительности отключается внедренная сущностью</t>
   </si>
   <si>
-    <t>, какая сбой началась среди африканских «мужиков</t>
-  </si>
-  <si>
-    <t>, какая сбой начался среди африканских «мужиков</t>
-  </si>
-  <si>
-    <t>чрезвычайную множества своей Установки</t>
-  </si>
-  <si>
-    <t>чрезвычайное множество своей Установки</t>
-  </si>
-  <si>
     <t>были заражены менингитоподобным заразой по всей</t>
   </si>
   <si>
@@ -2176,12 +1657,6 @@
     <t>неотъемлемым свойством вооружённых сил.</t>
   </si>
   <si>
-    <t>У био-роботов, согласно основному разработке Системы,</t>
-  </si>
-  <si>
-    <t>У био-роботов, согласно основной разработке Системы,</t>
-  </si>
-  <si>
     <t>Какая может быть согласование,</t>
   </si>
   <si>
@@ -2212,12 +1687,6 @@
     <t>постоянное перенапряжение.</t>
   </si>
   <si>
-    <t>через исконную целительство.</t>
-  </si>
-  <si>
-    <t>через исконное целительство.</t>
-  </si>
-  <si>
     <t>может повлечь за собой цепную ответ</t>
   </si>
   <si>
@@ -2230,24 +1699,12 @@
     <t>Подобное изменение необходимо</t>
   </si>
   <si>
-    <t xml:space="preserve">При изменения детородных возможностей </t>
-  </si>
-  <si>
-    <t xml:space="preserve">При изменении детородных возможностей </t>
-  </si>
-  <si>
     <t>установку Космического Жертвенности</t>
   </si>
   <si>
     <t>установку Космической Жертвенности</t>
   </si>
   <si>
-    <t>сразу на изменения вспоминают о</t>
-  </si>
-  <si>
-    <t>сразу на изменении вспоминают о</t>
-  </si>
-  <si>
     <t>помощь «братьям» в налаживания их</t>
   </si>
   <si>
@@ -2266,36 +1723,12 @@
     <t>в этом нелегком случае</t>
   </si>
   <si>
-    <t>ухудшении природных условиях беременность</t>
-  </si>
-  <si>
-    <t>ухудшении природных условий беременность</t>
-  </si>
-  <si>
     <t>в женской собеседования.</t>
   </si>
   <si>
     <t>в женском собеседовании</t>
   </si>
   <si>
-    <t>Это особа установка</t>
-  </si>
-  <si>
-    <t>Это особая  установка</t>
-  </si>
-  <si>
-    <t>скрывается весь тайна</t>
-  </si>
-  <si>
-    <t>скрывается вся тайна</t>
-  </si>
-  <si>
-    <t>устройстве крови вызывает мышечную запрет.</t>
-  </si>
-  <si>
-    <t>устройстве крови вызывает мышечный запрет.</t>
-  </si>
-  <si>
     <t>повышенного электро-притяжательного обстановки являются</t>
   </si>
   <si>
@@ -2314,36 +1747,18 @@
     <t>противоречит общепринятому мировоззрению</t>
   </si>
   <si>
-    <t>этой самой мировоззрения не противоречит</t>
-  </si>
-  <si>
-    <t>этому самому мировоззрению не противоречит</t>
-  </si>
-  <si>
     <t>же после вооружённые силы</t>
   </si>
   <si>
     <t>же после вооружённых сил</t>
   </si>
   <si>
-    <t>с записями беседа прошедших</t>
-  </si>
-  <si>
-    <t>с записями бесед прошедших</t>
-  </si>
-  <si>
     <t>Увлекательная сведения при этом была выявлена.</t>
   </si>
   <si>
     <t>Увлекательнае сведения при этом были выявлены.</t>
   </si>
   <si>
-    <t>своя, заранее определенная значение…</t>
-  </si>
-  <si>
-    <t>свое, заранее определенное значение…</t>
-  </si>
-  <si>
     <t>Многие целители в своей применении</t>
   </si>
   <si>
@@ -2354,54 +1769,6 @@
   </si>
   <si>
     <t>Общий чертёж проведения личного изменения с</t>
-  </si>
-  <si>
-    <t> покаяния изменение будет просто бессмысленна.</t>
-  </si>
-  <si>
-    <t> покаяния изменение будет просто бессмысленно</t>
-  </si>
-  <si>
-    <t>чем при личной изменения.</t>
-  </si>
-  <si>
-    <t>чем при личном изменении.</t>
-  </si>
-  <si>
-    <t>При проведении удалённой изменения </t>
-  </si>
-  <si>
-    <t>При проведении удалённого изменения </t>
-  </si>
-  <si>
-    <t>проведении удалённой изменения в любой ее образе</t>
-  </si>
-  <si>
-    <t>проведении удалённого изменения в любом ее образе</t>
-  </si>
-  <si>
-    <t>Вместо изменения по налаживания</t>
-  </si>
-  <si>
-    <t>Вместо изменения по налаживанию</t>
-  </si>
-  <si>
-    <t>При составление вездесущего предсказания</t>
-  </si>
-  <si>
-    <t>При составлении вездесущего предсказания</t>
-  </si>
-  <si>
-    <t>Обнародование в ростовских бумажным изданиях</t>
-  </si>
-  <si>
-    <t>Обнародование в ростовских бумажных изданиях</t>
-  </si>
-  <si>
-    <t>Мыслеобраза при проведении общей изменения</t>
-  </si>
-  <si>
-    <t>Мыслеобраза при проведении общего изменения</t>
   </si>
   <si>
     <t>выплеснула в космос всю накопленную заряд</t>
@@ -2488,7 +1855,7 @@
       <name val="LiberEmb"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2507,6 +1874,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2520,7 +1893,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2529,13 +1902,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2870,3071 +2247,2462 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157B4C6A-53EA-4FB9-AB5B-06694B8739E0}">
-  <dimension ref="A2:B431"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A4:B422"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="72" style="5" customWidth="1"/>
-    <col min="2" max="2" width="67.26953125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="67.26171875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="5" t="s">
-        <v>525</v>
-      </c>
-    </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>2</v>
-      </c>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="A5"/>
+      <c r="B5"/>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="A6"/>
+      <c r="B6"/>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>8</v>
+      <c r="A8" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="5" t="s">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>10</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>12</v>
+      <c r="A10" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>16</v>
+      <c r="A12" s="4" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>19</v>
+      <c r="A14" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="5" t="s">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>22</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>24</v>
+      <c r="A16" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="5" t="s">
-        <v>25</v>
+        <v>237</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>26</v>
+        <v>238</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>28</v>
+      <c r="A18" t="s">
+        <v>424</v>
+      </c>
+      <c r="B18" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>30</v>
+      <c r="A19" t="s">
+        <v>508</v>
+      </c>
+      <c r="B19" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="5" t="s">
-        <v>31</v>
+        <v>233</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>32</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>34</v>
+      <c r="A21" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>36</v>
+      <c r="A22" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>38</v>
+      <c r="A23" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>40</v>
+      <c r="A24" t="s">
+        <v>554</v>
+      </c>
+      <c r="B24" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="5" t="s">
-        <v>41</v>
+        <v>167</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>42</v>
+        <v>168</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="5" t="s">
-        <v>43</v>
+        <v>205</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>44</v>
+        <v>206</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="5" t="s">
-        <v>45</v>
+        <v>291</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>46</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="5" t="s">
-        <v>47</v>
+        <v>235</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>48</v>
+        <v>236</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="5" t="s">
-        <v>49</v>
+        <v>270</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>50</v>
+        <v>269</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>52</v>
+      <c r="A30" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>54</v>
+      <c r="A31" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="5" t="s">
-        <v>56</v>
+        <v>141</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="5" t="s">
-        <v>57</v>
+        <v>211</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>58</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="5" t="s">
-        <v>59</v>
+        <v>201</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>60</v>
+        <v>202</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="5" t="s">
-        <v>61</v>
+        <v>221</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>62</v>
+        <v>222</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="5" t="s">
-        <v>63</v>
+        <v>213</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>64</v>
+        <v>214</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>66</v>
+      <c r="A37" t="s">
+        <v>446</v>
+      </c>
+      <c r="B37" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>68</v>
+      <c r="A38" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="5" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="5" t="s">
-        <v>71</v>
+        <v>165</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>74</v>
+      <c r="A41" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>75</v>
+      <c r="A42" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="5" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="5" t="s">
-        <v>79</v>
+        <v>143</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>80</v>
+        <v>144</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>82</v>
+      <c r="A45" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="5" t="s">
-        <v>83</v>
+        <v>197</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>84</v>
+        <v>198</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>86</v>
+      <c r="A47" t="s">
+        <v>197</v>
+      </c>
+      <c r="B47" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="5" t="s">
-        <v>87</v>
+        <v>203</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>88</v>
+        <v>204</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>90</v>
+      <c r="A49" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="5" t="s">
-        <v>92</v>
+        <v>217</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>91</v>
+        <v>218</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="5" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="5" t="s">
-        <v>95</v>
+        <v>307</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>96</v>
+        <v>308</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="5" t="s">
-        <v>97</v>
+        <v>195</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>98</v>
+        <v>196</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>100</v>
+      <c r="A54" t="s">
+        <v>500</v>
+      </c>
+      <c r="B54" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="5" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>104</v>
+      <c r="A56" t="s">
+        <v>536</v>
+      </c>
+      <c r="B56" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="5" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="5" t="s">
-        <v>107</v>
+        <v>335</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>108</v>
+        <v>336</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="5" t="s">
-        <v>109</v>
+        <v>33</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>110</v>
+        <v>34</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="5" t="s">
-        <v>111</v>
+        <v>9</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>112</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="5" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>114</v>
+        <v>156</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="5" t="s">
-        <v>115</v>
+        <v>528</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>116</v>
+        <v>529</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>118</v>
+      <c r="A63" t="s">
+        <v>522</v>
+      </c>
+      <c r="B63" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="5" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B66" s="5" t="s">
         <v>123</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="5" t="s">
-        <v>125</v>
+        <v>349</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>126</v>
+        <v>350</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="5" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>130</v>
+      <c r="A69" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="5" t="s">
-        <v>131</v>
+        <v>223</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>132</v>
+        <v>224</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>134</v>
+      <c r="A71" t="s">
+        <v>496</v>
+      </c>
+      <c r="B71" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="5" t="s">
-        <v>135</v>
+        <v>207</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>136</v>
+        <v>208</v>
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>138</v>
+      <c r="A73" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>571</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="5" t="s">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>140</v>
+        <v>76</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="5" t="s">
-        <v>141</v>
+        <v>229</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>142</v>
+        <v>230</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="5" t="s">
-        <v>143</v>
+        <v>273</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>144</v>
+        <v>274</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="5" t="s">
-        <v>145</v>
+        <v>364</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>146</v>
+        <v>363</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="5" t="s">
-        <v>147</v>
+        <v>408</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>148</v>
+        <v>409</v>
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>150</v>
+      <c r="A79" t="s">
+        <v>420</v>
+      </c>
+      <c r="B79" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="5" t="s">
-        <v>151</v>
+        <v>281</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>152</v>
+        <v>282</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="5" t="s">
-        <v>153</v>
+        <v>255</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>154</v>
+        <v>256</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>156</v>
+      <c r="A82" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="5" t="s">
-        <v>157</v>
+        <v>331</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>158</v>
+        <v>332</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="5" t="s">
-        <v>159</v>
+        <v>109</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>160</v>
+        <v>110</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="5" t="s">
-        <v>162</v>
+        <v>383</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>161</v>
+        <v>384</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="B86" s="5" t="s">
-        <v>164</v>
+      <c r="A86" t="s">
+        <v>506</v>
+      </c>
+      <c r="B86" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>166</v>
+      <c r="A87" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="5" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>167</v>
+        <v>118</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="5" t="s">
-        <v>169</v>
+        <v>271</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>170</v>
+        <v>272</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="5" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="5" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>174</v>
+        <v>26</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B92" s="5" t="s">
-        <v>176</v>
+      <c r="A92" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="5" t="s">
-        <v>177</v>
+        <v>284</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>178</v>
+        <v>283</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="5" t="s">
-        <v>179</v>
+        <v>85</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>180</v>
+        <v>86</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="5" t="s">
-        <v>181</v>
+        <v>285</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>182</v>
+        <v>286</v>
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="B96" s="5" t="s">
-        <v>184</v>
+      <c r="A96" t="s">
+        <v>562</v>
+      </c>
+      <c r="B96" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="5" t="s">
-        <v>185</v>
+        <v>225</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>186</v>
+        <v>226</v>
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="B98" s="5" t="s">
-        <v>188</v>
+      <c r="A98" t="s">
+        <v>510</v>
+      </c>
+      <c r="B98" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="5" t="s">
-        <v>189</v>
+        <v>29</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>190</v>
+        <v>30</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="5" t="s">
-        <v>191</v>
+        <v>341</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>192</v>
+        <v>342</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="5" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B102" s="5" t="s">
-        <v>196</v>
+      <c r="A102" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="5" t="s">
-        <v>197</v>
+        <v>83</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>198</v>
+        <v>84</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="5" t="s">
-        <v>199</v>
+        <v>157</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>200</v>
+        <v>158</v>
       </c>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="B105" s="5" t="s">
-        <v>202</v>
+      <c r="A105" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="106" spans="1:2">
-      <c r="A106" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="B106" s="5" t="s">
-        <v>203</v>
+      <c r="A106" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="5" t="s">
-        <v>205</v>
+        <v>289</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>206</v>
+        <v>290</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="5" t="s">
-        <v>207</v>
+        <v>325</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>208</v>
+        <v>326</v>
       </c>
     </row>
     <row r="109" spans="1:2">
-      <c r="A109" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="B109" s="5" t="s">
-        <v>210</v>
+      <c r="A109" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="5" t="s">
-        <v>211</v>
+        <v>177</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>212</v>
+        <v>178</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="5" t="s">
-        <v>213</v>
+        <v>125</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>214</v>
+        <v>126</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="5" t="s">
-        <v>215</v>
+        <v>179</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>216</v>
+        <v>180</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="5" t="s">
-        <v>217</v>
+        <v>21</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>218</v>
+        <v>22</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="5" t="s">
-        <v>219</v>
+        <v>357</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>220</v>
+        <v>358</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="5" t="s">
-        <v>221</v>
+        <v>514</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>222</v>
+        <v>515</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="5" t="s">
-        <v>223</v>
+        <v>277</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2">
-      <c r="A117" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>225</v>
+        <v>278</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" ht="15.3">
+      <c r="A117" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="5" t="s">
-        <v>227</v>
+        <v>27</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>228</v>
+        <v>28</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="5" t="s">
-        <v>229</v>
+        <v>121</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>230</v>
+        <v>122</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="5" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="5" t="s">
-        <v>233</v>
+        <v>153</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>234</v>
+        <v>154</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="5" t="s">
-        <v>235</v>
+        <v>59</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>236</v>
+        <v>60</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="5" t="s">
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>238</v>
+        <v>210</v>
       </c>
     </row>
     <row r="124" spans="1:2">
-      <c r="A124" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="B124" s="5" t="s">
-        <v>240</v>
+      <c r="A124" t="s">
+        <v>468</v>
+      </c>
+      <c r="B124" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="125" spans="1:2">
-      <c r="A125" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="B125" s="5" t="s">
-        <v>242</v>
+      <c r="A125" t="s">
+        <v>412</v>
+      </c>
+      <c r="B125" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="5" t="s">
-        <v>243</v>
+        <v>23</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2">
-      <c r="A127" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="B127" s="5" t="s">
-        <v>246</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" ht="17.7">
+      <c r="A127" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="128" spans="1:2">
-      <c r="A128" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="B128" s="5" t="s">
-        <v>247</v>
+      <c r="A128" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="5" t="s">
-        <v>249</v>
+        <v>502</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>250</v>
+        <v>503</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="5" t="s">
-        <v>251</v>
+        <v>199</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>252</v>
+        <v>200</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="5" t="s">
-        <v>253</v>
+        <v>516</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>254</v>
+        <v>517</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="5" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B133" s="5" t="s">
-        <v>258</v>
+      <c r="A133" t="s">
+        <v>392</v>
+      </c>
+      <c r="B133" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="5" t="s">
-        <v>259</v>
+        <v>301</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>260</v>
+        <v>302</v>
       </c>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="B135" s="5" t="s">
-        <v>262</v>
+      <c r="A135" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="5" t="s">
-        <v>263</v>
+        <v>120</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>264</v>
+        <v>119</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="5" t="s">
-        <v>265</v>
+        <v>41</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>266</v>
+        <v>42</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="5" t="s">
-        <v>267</v>
+        <v>111</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>268</v>
+        <v>112</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="5" t="s">
-        <v>269</v>
+        <v>151</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>270</v>
+        <v>152</v>
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="B140" s="5" t="s">
-        <v>272</v>
+      <c r="A140" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="5" t="s">
-        <v>273</v>
+        <v>175</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>274</v>
+        <v>176</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="B142" s="5" t="s">
-        <v>276</v>
+      <c r="A142" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="5" t="s">
-        <v>277</v>
+        <v>139</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>278</v>
+        <v>140</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="5" t="s">
-        <v>279</v>
+        <v>361</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>280</v>
+        <v>362</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="5" t="s">
-        <v>281</v>
+        <v>191</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>282</v>
+        <v>192</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="5" t="s">
-        <v>283</v>
+        <v>137</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>284</v>
+        <v>138</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="B147" s="5" t="s">
-        <v>286</v>
+      <c r="A147" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="5" t="s">
-        <v>287</v>
+        <v>486</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>288</v>
+        <v>487</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="B149" s="5" t="s">
-        <v>290</v>
+      <c r="A149" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="B150" s="5" t="s">
-        <v>292</v>
+      <c r="A150" t="s">
+        <v>474</v>
+      </c>
+      <c r="B150" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="5" t="s">
-        <v>293</v>
+        <v>470</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>294</v>
+        <v>471</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="5" t="s">
-        <v>295</v>
+        <v>249</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>296</v>
+        <v>250</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="B153" s="5" t="s">
-        <v>298</v>
+      <c r="A153" t="s">
+        <v>440</v>
+      </c>
+      <c r="B153" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="B154" s="5" t="s">
-        <v>300</v>
+      <c r="A154" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="B155" s="5" t="s">
-        <v>302</v>
+      <c r="A155" t="s">
+        <v>394</v>
+      </c>
+      <c r="B155" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="5" t="s">
-        <v>303</v>
+        <v>193</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>304</v>
+        <v>194</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="B157" s="5" t="s">
-        <v>306</v>
+      <c r="A157" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="B157" s="7" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="5" t="s">
-        <v>307</v>
+        <v>65</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>308</v>
+        <v>66</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="B159" s="5" t="s">
-        <v>310</v>
+      <c r="A159" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="B159" s="9" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="B160" s="5" t="s">
-        <v>312</v>
+      <c r="A160" t="s">
+        <v>400</v>
+      </c>
+      <c r="B160" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="B161" s="5" t="s">
-        <v>314</v>
+      <c r="A161" t="s">
+        <v>444</v>
+      </c>
+      <c r="B161" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="B162" s="5" t="s">
-        <v>316</v>
+      <c r="A162" t="s">
+        <v>566</v>
+      </c>
+      <c r="B162" t="s">
+        <v>567</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="5" t="s">
-        <v>317</v>
+        <v>245</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>318</v>
+        <v>246</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="B164" s="5" t="s">
-        <v>320</v>
+      <c r="A164" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="B164" s="7" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="B165" s="5" t="s">
-        <v>322</v>
+      <c r="A165" t="s">
+        <v>542</v>
+      </c>
+      <c r="B165" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="B166" s="5" t="s">
-        <v>324</v>
+      <c r="A166" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="B166" s="7" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="5" t="s">
-        <v>325</v>
+        <v>265</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>326</v>
+        <v>266</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="5" t="s">
-        <v>327</v>
+        <v>40</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>328</v>
+        <v>39</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="B169" s="5" t="s">
-        <v>330</v>
+      <c r="A169" t="s">
+        <v>423</v>
+      </c>
+      <c r="B169" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="5" t="s">
-        <v>331</v>
+        <v>31</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>332</v>
+        <v>32</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="5" t="s">
-        <v>333</v>
+        <v>129</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>334</v>
+        <v>130</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="5" t="s">
-        <v>335</v>
+        <v>279</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>336</v>
+        <v>280</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="5" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>338</v>
+        <v>320</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="5" t="s">
-        <v>339</v>
+        <v>293</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>340</v>
+        <v>294</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="5" t="s">
-        <v>341</v>
+        <v>241</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>342</v>
+        <v>242</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="B176" s="5" t="s">
-        <v>344</v>
+      <c r="A176" t="s">
+        <v>494</v>
+      </c>
+      <c r="B176" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="5" t="s">
-        <v>345</v>
+        <v>49</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>346</v>
+        <v>50</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="B178" s="5" t="s">
+      <c r="B179" s="7" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="179" spans="1:2">
-      <c r="A179" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="B179" s="5" t="s">
-        <v>350</v>
-      </c>
-    </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="B180" s="5" t="s">
-        <v>352</v>
+      <c r="A180" t="s">
+        <v>498</v>
+      </c>
+      <c r="B180" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="B181" s="5" t="s">
-        <v>354</v>
+      <c r="A181" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="B181" s="7" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="B182" s="5" t="s">
-        <v>356</v>
+      <c r="A182" t="s">
+        <v>534</v>
+      </c>
+      <c r="B182" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="B183" s="5" t="s">
-        <v>358</v>
+      <c r="A183" t="s">
+        <v>456</v>
+      </c>
+      <c r="B183" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="5" t="s">
-        <v>359</v>
+        <v>35</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>360</v>
+        <v>36</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="B185" s="5" t="s">
-        <v>362</v>
+      <c r="A185" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="5" t="s">
-        <v>363</v>
+        <v>72</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>364</v>
+        <v>71</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="5" t="s">
-        <v>365</v>
+        <v>64</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>366</v>
+        <v>63</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="5" t="s">
-        <v>367</v>
+        <v>251</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>368</v>
+        <v>252</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="5" t="s">
-        <v>369</v>
+        <v>231</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>370</v>
+        <v>232</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="5" t="s">
-        <v>371</v>
+        <v>259</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>372</v>
+        <v>260</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="5" t="s">
-        <v>373</v>
+        <v>275</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>374</v>
+        <v>276</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="5" t="s">
-        <v>376</v>
+        <v>287</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>375</v>
+        <v>288</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="5" t="s">
-        <v>377</v>
+        <v>267</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>378</v>
+        <v>268</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="B194" s="5" t="s">
-        <v>380</v>
+      <c r="A194" t="s">
+        <v>480</v>
+      </c>
+      <c r="B194" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="195" spans="1:2">
       <c r="A195" s="5" t="s">
-        <v>381</v>
+        <v>67</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>382</v>
+        <v>68</v>
       </c>
     </row>
     <row r="196" spans="1:2">
       <c r="A196" s="5" t="s">
-        <v>383</v>
+        <v>88</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>384</v>
+        <v>87</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="B197" s="5" t="s">
-        <v>386</v>
+      <c r="A197" t="s">
+        <v>390</v>
+      </c>
+      <c r="B197" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="198" spans="1:2">
       <c r="A198" s="5" t="s">
-        <v>387</v>
+        <v>181</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>388</v>
+        <v>182</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="B199" s="5" t="s">
-        <v>389</v>
+      <c r="A199" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="200" spans="1:2">
       <c r="A200" s="5" t="s">
-        <v>391</v>
+        <v>145</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>392</v>
+        <v>146</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="B201" s="5" t="s">
-        <v>394</v>
+      <c r="A201" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="B202" s="5" t="s">
-        <v>396</v>
+      <c r="A202" t="s">
+        <v>406</v>
+      </c>
+      <c r="B202" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="A203" s="5" t="s">
-        <v>397</v>
+        <v>79</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>398</v>
+        <v>80</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="A204" s="5" t="s">
-        <v>399</v>
+        <v>91</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>400</v>
+        <v>92</v>
       </c>
     </row>
     <row r="205" spans="1:2">
       <c r="A205" s="5" t="s">
-        <v>401</v>
+        <v>504</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2" ht="15.5">
-      <c r="A206" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="B206" s="1" t="s">
-        <v>404</v>
+        <v>505</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B206" s="5" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="5" t="s">
-        <v>405</v>
-      </c>
-      <c r="B207" s="5" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2" ht="15.5">
-      <c r="A208" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="B208" s="1" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2" ht="15.5">
-      <c r="A209" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="B209" s="1" t="s">
-        <v>410</v>
+      <c r="A207" t="s">
+        <v>488</v>
+      </c>
+      <c r="B207" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="B210" s="5" t="s">
-        <v>412</v>
+      <c r="A210" t="s">
+        <v>452</v>
+      </c>
+      <c r="B210" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="B211" s="5" t="s">
-        <v>414</v>
+      <c r="A211" t="s">
+        <v>568</v>
+      </c>
+      <c r="B211" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="212" spans="1:2">
       <c r="A212" s="5" t="s">
-        <v>415</v>
+        <v>17</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>416</v>
+        <v>18</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="B213" s="5" t="s">
-        <v>418</v>
+      <c r="A213" t="s">
+        <v>512</v>
+      </c>
+      <c r="B213" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B214" s="7" t="s">
-        <v>420</v>
+      <c r="A214" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="B215" s="5" t="s">
-        <v>422</v>
+      <c r="A215" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="B215" s="7" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="B216" s="5" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2" ht="18">
-      <c r="A217" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="B217" s="2" t="s">
-        <v>426</v>
+      <c r="A216" t="s">
+        <v>410</v>
+      </c>
+      <c r="B216" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B217" s="5" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="218" spans="1:2">
       <c r="A218" s="5" t="s">
-        <v>427</v>
+        <v>53</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="219" spans="1:2">
-      <c r="A219" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="B219" s="7" t="s">
-        <v>430</v>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" ht="15.3">
+      <c r="A219" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220" s="5" t="s">
-        <v>431</v>
+        <v>73</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>432</v>
+        <v>74</v>
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="7" t="s">
-        <v>433</v>
-      </c>
-      <c r="B221" s="7" t="s">
-        <v>434</v>
+      <c r="A221" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="222" spans="1:2">
       <c r="A222" s="5" t="s">
-        <v>435</v>
+        <v>103</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>436</v>
+        <v>104</v>
       </c>
     </row>
     <row r="223" spans="1:2">
       <c r="A223" s="5" t="s">
-        <v>437</v>
+        <v>299</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>438</v>
+        <v>300</v>
       </c>
     </row>
     <row r="224" spans="1:2">
       <c r="A224" s="5" t="s">
-        <v>439</v>
+        <v>219</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>440</v>
+        <v>220</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" s="5" t="s">
-        <v>441</v>
+        <v>263</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>442</v>
+        <v>264</v>
       </c>
     </row>
     <row r="226" spans="1:2">
-      <c r="A226" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="B226" s="5" t="s">
-        <v>444</v>
+      <c r="A226" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="B226" s="7" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="227" spans="1:2">
-      <c r="A227" s="7" t="s">
-        <v>445</v>
-      </c>
-      <c r="B227" s="7" t="s">
-        <v>446</v>
+      <c r="A227" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="228" spans="1:2">
       <c r="A228" s="5" t="s">
-        <v>447</v>
+        <v>355</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>448</v>
+        <v>356</v>
       </c>
     </row>
     <row r="229" spans="1:2">
-      <c r="A229" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="B229" s="7" t="s">
-        <v>450</v>
+      <c r="A229" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="B230" s="5" t="s">
-        <v>452</v>
+      <c r="A230" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="B231" s="5" t="s">
-        <v>454</v>
+      <c r="A231" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="B231" s="7" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="B232" s="7" t="s">
-        <v>456</v>
+      <c r="A232" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" s="7" t="s">
-        <v>457</v>
-      </c>
-      <c r="B233" s="7" t="s">
-        <v>458</v>
+      <c r="A233" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="234" spans="1:2">
-      <c r="A234" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="B234" s="5" t="s">
-        <v>460</v>
+      <c r="A234" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="235" spans="1:2">
       <c r="A235" s="5" t="s">
-        <v>461</v>
+        <v>321</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>462</v>
+        <v>322</v>
       </c>
     </row>
     <row r="236" spans="1:2">
-      <c r="A236" s="7" t="s">
-        <v>463</v>
-      </c>
-      <c r="B236" s="7" t="s">
-        <v>464</v>
+      <c r="A236" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B236" s="5" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="237" spans="1:2">
-      <c r="A237" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="B237" s="7" t="s">
-        <v>466</v>
+      <c r="A237" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B237" s="5" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="238" spans="1:2">
       <c r="A238" s="5" t="s">
-        <v>467</v>
+        <v>51</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>468</v>
+        <v>52</v>
       </c>
     </row>
     <row r="239" spans="1:2">
-      <c r="A239" s="7" t="s">
-        <v>469</v>
-      </c>
-      <c r="B239" s="7" t="s">
-        <v>470</v>
+      <c r="A239" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="240" spans="1:2">
-      <c r="A240" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="B240" s="7" t="s">
-        <v>472</v>
+      <c r="A240" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B240" s="5" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="241" spans="1:2">
-      <c r="A241" s="7" t="s">
-        <v>473</v>
-      </c>
-      <c r="B241" s="7" t="s">
-        <v>474</v>
+      <c r="A241" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="242" spans="1:2">
       <c r="A242" s="5" t="s">
-        <v>475</v>
+        <v>187</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>476</v>
+        <v>188</v>
       </c>
     </row>
     <row r="243" spans="1:2">
-      <c r="A243" s="7" t="s">
-        <v>477</v>
-      </c>
-      <c r="B243" s="7" t="s">
-        <v>478</v>
+      <c r="A243" t="s">
+        <v>556</v>
+      </c>
+      <c r="B243" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="244" spans="1:2">
-      <c r="A244" s="7" t="s">
-        <v>479</v>
-      </c>
-      <c r="B244" s="7" t="s">
-        <v>480</v>
+      <c r="A244" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B244" s="5" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="245" spans="1:2">
-      <c r="A245" s="5" t="s">
-        <v>481</v>
-      </c>
-      <c r="B245" s="5" t="s">
-        <v>482</v>
+      <c r="A245" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="246" spans="1:2">
       <c r="A246" s="5" t="s">
-        <v>483</v>
+        <v>323</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>484</v>
+        <v>324</v>
       </c>
     </row>
     <row r="247" spans="1:2">
-      <c r="A247" s="7" t="s">
-        <v>485</v>
-      </c>
-      <c r="B247" s="7" t="s">
-        <v>486</v>
+      <c r="A247" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="B247" s="9" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="248" spans="1:2">
-      <c r="A248" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="B248" s="5" t="s">
-        <v>488</v>
+      <c r="A248" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="249" spans="1:2">
-      <c r="A249" s="5" t="s">
-        <v>489</v>
-      </c>
-      <c r="B249" s="5" t="s">
-        <v>490</v>
+      <c r="A249" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="B249" s="3" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="250" spans="1:2">
       <c r="A250" s="5" t="s">
-        <v>492</v>
+        <v>183</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>491</v>
+        <v>184</v>
       </c>
     </row>
     <row r="251" spans="1:2">
-      <c r="A251" s="7" t="s">
-        <v>493</v>
-      </c>
-      <c r="B251" s="7" t="s">
-        <v>494</v>
+      <c r="A251" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B251" s="5" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="252" spans="1:2">
-      <c r="A252" s="7" t="s">
-        <v>495</v>
-      </c>
-      <c r="B252" s="7" t="s">
-        <v>496</v>
+      <c r="A252" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="B252" s="9" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" s="5" t="s">
-        <v>497</v>
+        <v>101</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>498</v>
+        <v>102</v>
       </c>
     </row>
     <row r="254" spans="1:2">
-      <c r="A254" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="B254" s="7" t="s">
-        <v>500</v>
+      <c r="A254" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="B254" s="5" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="255" spans="1:2">
       <c r="A255" s="5" t="s">
-        <v>501</v>
+        <v>385</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>502</v>
+        <v>386</v>
       </c>
     </row>
     <row r="256" spans="1:2">
-      <c r="A256" s="7" t="s">
-        <v>503</v>
-      </c>
-      <c r="B256" s="7" t="s">
-        <v>504</v>
+      <c r="A256" t="s">
+        <v>548</v>
+      </c>
+      <c r="B256" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="257" spans="1:2">
-      <c r="A257" s="7" t="s">
-        <v>505</v>
-      </c>
-      <c r="B257" s="7" t="s">
-        <v>506</v>
+      <c r="A257" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="B257" s="9" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="258" spans="1:2">
-      <c r="A258" s="7" t="s">
-        <v>507</v>
-      </c>
-      <c r="B258" s="7" t="s">
-        <v>508</v>
+      <c r="A258" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="B258" s="3" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="259" spans="1:2">
-      <c r="A259" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="B259" s="7" t="s">
-        <v>509</v>
+      <c r="A259" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B259" s="5" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="260" spans="1:2">
-      <c r="A260" s="7" t="s">
-        <v>511</v>
-      </c>
-      <c r="B260" s="7" t="s">
-        <v>512</v>
+      <c r="A260" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B260" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="261" spans="1:2">
-      <c r="A261" s="7" t="s">
-        <v>513</v>
-      </c>
-      <c r="B261" s="7" t="s">
-        <v>514</v>
+      <c r="A261" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B261" s="5" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="262" spans="1:2">
-      <c r="A262" s="7" t="s">
-        <v>515</v>
-      </c>
-      <c r="B262" s="7" t="s">
-        <v>516</v>
+      <c r="A262" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="B262" s="3" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="263" spans="1:2">
-      <c r="A263" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="B263" s="7" t="s">
-        <v>518</v>
+      <c r="A263" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="B263" s="5" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="264" spans="1:2">
       <c r="A264" s="5" t="s">
-        <v>519</v>
+        <v>169</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>520</v>
+        <v>170</v>
       </c>
     </row>
     <row r="265" spans="1:2">
-      <c r="A265" s="5" t="s">
-        <v>521</v>
-      </c>
-      <c r="B265" s="5" t="s">
-        <v>522</v>
+      <c r="A265" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B265" s="3" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="266" spans="1:2">
-      <c r="A266" s="7" t="s">
-        <v>523</v>
-      </c>
-      <c r="B266" s="7" t="s">
-        <v>524</v>
+      <c r="A266" t="s">
+        <v>558</v>
+      </c>
+      <c r="B266" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="267" spans="1:2">
-      <c r="A267" s="3" t="s">
-        <v>526</v>
-      </c>
-      <c r="B267" s="3" t="s">
-        <v>527</v>
+      <c r="A267" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B267" s="5" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="268" spans="1:2">
       <c r="A268" s="5" t="s">
-        <v>528</v>
+        <v>7</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>529</v>
+        <v>8</v>
       </c>
     </row>
     <row r="269" spans="1:2">
-      <c r="A269" t="s">
-        <v>530</v>
-      </c>
-      <c r="B269" t="s">
-        <v>531</v>
+      <c r="A269" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B269" s="3" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="270" spans="1:2">
-      <c r="A270" t="s">
-        <v>532</v>
-      </c>
-      <c r="B270" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="271" spans="1:2">
-      <c r="A271" t="s">
-        <v>534</v>
-      </c>
-      <c r="B271" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="272" spans="1:2">
-      <c r="A272" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="B272" s="3" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="273" spans="1:2">
-      <c r="A273" t="s">
-        <v>538</v>
-      </c>
-      <c r="B273" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="274" spans="1:2">
-      <c r="A274" t="s">
-        <v>540</v>
-      </c>
-      <c r="B274" t="s">
-        <v>541</v>
+      <c r="A270" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="B270" s="7" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="275" spans="1:2">
-      <c r="A275" s="3" t="s">
-        <v>542</v>
-      </c>
-      <c r="B275" s="3" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="276" spans="1:2">
-      <c r="A276" s="3" t="s">
-        <v>544</v>
-      </c>
-      <c r="B276" s="3" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="277" spans="1:2">
-      <c r="A277" t="s">
+      <c r="A275" s="3"/>
+      <c r="B275" s="3"/>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279" s="7"/>
+      <c r="B279" s="7"/>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="B280" s="5" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281" s="7"/>
+      <c r="B281" s="7"/>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285"/>
+      <c r="B285"/>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286" s="3"/>
+      <c r="B286" s="3"/>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288" s="3"/>
+      <c r="B288" s="3"/>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289" s="7"/>
+      <c r="B289" s="7"/>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="B292" s="3" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="B293" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294" s="16"/>
+      <c r="B294" s="16"/>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295" s="3"/>
+      <c r="B295" s="3"/>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B296" s="5" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297" s="5" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B298" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299" s="3"/>
+      <c r="B299" s="3"/>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B300" s="5" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B301" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B304" s="5" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B305" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306" s="7"/>
+      <c r="B306" s="7"/>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308" s="3"/>
+      <c r="B308" s="3"/>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310"/>
+      <c r="B310"/>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B314" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315" s="3"/>
+      <c r="B315" s="3"/>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324" s="8"/>
+      <c r="B324" s="8"/>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326" s="7"/>
+      <c r="B326" s="7"/>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328"/>
+      <c r="B328"/>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334" s="3"/>
+      <c r="B334" s="3"/>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337"/>
+      <c r="B337"/>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341"/>
+      <c r="B341"/>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343" s="15"/>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344"/>
+      <c r="B344"/>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346" s="3"/>
+      <c r="B346" s="3"/>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B348" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349" s="13" t="s">
+        <v>564</v>
+      </c>
+      <c r="B349" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351" s="7"/>
+      <c r="B351" s="7"/>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352"/>
+      <c r="B352"/>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353" s="14" t="s">
+        <v>434</v>
+      </c>
+      <c r="B353" s="3" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354" s="13" t="s">
         <v>546</v>
       </c>
-      <c r="B277" t="s">
+      <c r="B354" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="278" spans="1:2">
-      <c r="A278" t="s">
-        <v>548</v>
-      </c>
-      <c r="B278" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="279" spans="1:2">
-      <c r="A279" s="5" t="s">
-        <v>550</v>
-      </c>
-      <c r="B279" s="5" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="280" spans="1:2">
-      <c r="A280" t="s">
-        <v>552</v>
-      </c>
-      <c r="B280" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="281" spans="1:2">
-      <c r="A281" t="s">
-        <v>554</v>
-      </c>
-      <c r="B281" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="282" spans="1:2">
-      <c r="A282" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="B282" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="283" spans="1:2">
-      <c r="A283" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="B283" s="3" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="284" spans="1:2">
-      <c r="A284" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="B284" s="3" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="285" spans="1:2">
-      <c r="A285" t="s">
-        <v>562</v>
-      </c>
-      <c r="B285" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="286" spans="1:2">
-      <c r="A286" t="s">
-        <v>564</v>
-      </c>
-      <c r="B286" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="287" spans="1:2">
-      <c r="A287" t="s">
-        <v>567</v>
-      </c>
-      <c r="B287" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="288" spans="1:2">
-      <c r="A288" t="s">
-        <v>568</v>
-      </c>
-      <c r="B288" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="289" spans="1:2">
-      <c r="A289" t="s">
-        <v>570</v>
-      </c>
-      <c r="B289" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="290" spans="1:2">
-      <c r="A290" s="3" t="s">
-        <v>572</v>
-      </c>
-      <c r="B290" s="3" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="291" spans="1:2">
-      <c r="A291" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="B291" s="3" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="292" spans="1:2">
-      <c r="A292" s="9" t="s">
-        <v>576</v>
-      </c>
-      <c r="B292" s="9" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="293" spans="1:2">
-      <c r="A293" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="B293" s="3" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="294" spans="1:2">
-      <c r="A294" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="B294" s="3" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="295" spans="1:2">
-      <c r="A295" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="B295" s="3" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="296" spans="1:2">
-      <c r="A296" s="3" t="s">
-        <v>584</v>
-      </c>
-      <c r="B296" s="3" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="297" spans="1:2">
-      <c r="A297" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="B297" s="3" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="298" spans="1:2">
-      <c r="A298" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="B298" s="3" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="299" spans="1:2">
-      <c r="A299" t="s">
-        <v>590</v>
-      </c>
-      <c r="B299" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="300" spans="1:2">
-      <c r="A300" t="s">
-        <v>592</v>
-      </c>
-      <c r="B300" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="301" spans="1:2">
-      <c r="A301" t="s">
-        <v>594</v>
-      </c>
-      <c r="B301" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="302" spans="1:2">
-      <c r="A302" t="s">
-        <v>596</v>
-      </c>
-      <c r="B302" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="303" spans="1:2">
-      <c r="A303" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="B303" s="3" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="304" spans="1:2">
-      <c r="A304" t="s">
-        <v>600</v>
-      </c>
-      <c r="B304" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="305" spans="1:2">
-      <c r="A305" s="3" t="s">
-        <v>602</v>
-      </c>
-      <c r="B305" s="3" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="306" spans="1:2">
-      <c r="A306" t="s">
-        <v>604</v>
-      </c>
-      <c r="B306" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="307" spans="1:2">
-      <c r="A307" s="10" t="s">
-        <v>606</v>
-      </c>
-      <c r="B307" s="10" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="308" spans="1:2">
-      <c r="A308" s="10" t="s">
-        <v>608</v>
-      </c>
-      <c r="B308" s="10" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="309" spans="1:2">
-      <c r="A309" t="s">
-        <v>610</v>
-      </c>
-      <c r="B309" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="310" spans="1:2">
-      <c r="A310" t="s">
-        <v>612</v>
-      </c>
-      <c r="B310" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="311" spans="1:2">
-      <c r="A311" t="s">
-        <v>614</v>
-      </c>
-      <c r="B311" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="312" spans="1:2">
-      <c r="A312" t="s">
-        <v>616</v>
-      </c>
-      <c r="B312" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="313" spans="1:2">
-      <c r="A313" s="10" t="s">
-        <v>618</v>
-      </c>
-      <c r="B313" s="10" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="314" spans="1:2">
-      <c r="A314" s="3" t="s">
-        <v>620</v>
-      </c>
-      <c r="B314" s="3" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="315" spans="1:2">
-      <c r="A315" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="B315" s="3" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="316" spans="1:2">
-      <c r="A316" s="3" t="s">
-        <v>624</v>
-      </c>
-      <c r="B316" s="3" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="317" spans="1:2">
-      <c r="A317" s="10" t="s">
-        <v>626</v>
-      </c>
-      <c r="B317" s="10" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="318" spans="1:2">
-      <c r="A318" t="s">
-        <v>628</v>
-      </c>
-      <c r="B318" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="319" spans="1:2">
-      <c r="A319" s="3" t="s">
-        <v>630</v>
-      </c>
-      <c r="B319" s="3" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="320" spans="1:2">
-      <c r="A320" s="5" t="s">
-        <v>632</v>
-      </c>
-      <c r="B320" s="5" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="321" spans="1:2">
-      <c r="A321" s="10" t="s">
-        <v>634</v>
-      </c>
-      <c r="B321" s="10" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="322" spans="1:2">
-      <c r="A322" t="s">
-        <v>636</v>
-      </c>
-      <c r="B322" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="323" spans="1:2">
-      <c r="A323" s="3" t="s">
-        <v>638</v>
-      </c>
-      <c r="B323" s="3" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="324" spans="1:2">
-      <c r="A324" s="3" t="s">
-        <v>640</v>
-      </c>
-      <c r="B324" s="3" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="325" spans="1:2">
-      <c r="A325" t="s">
-        <v>642</v>
-      </c>
-      <c r="B325" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="326" spans="1:2">
-      <c r="A326" s="3" t="s">
-        <v>644</v>
-      </c>
-      <c r="B326" s="3" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="327" spans="1:2">
-      <c r="A327" s="5" t="s">
-        <v>646</v>
-      </c>
-      <c r="B327" s="5" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="328" spans="1:2">
-      <c r="A328" s="5" t="s">
-        <v>648</v>
-      </c>
-      <c r="B328" s="5" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="329" spans="1:2">
-      <c r="A329" t="s">
-        <v>650</v>
-      </c>
-      <c r="B329" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="330" spans="1:2">
-      <c r="A330" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="B330" s="3" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="331" spans="1:2">
-      <c r="A331" s="5" t="s">
-        <v>654</v>
-      </c>
-      <c r="B331" s="5" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="332" spans="1:2">
-      <c r="A332" s="3" t="s">
-        <v>656</v>
-      </c>
-      <c r="B332" s="3" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="333" spans="1:2">
-      <c r="A333" t="s">
-        <v>658</v>
-      </c>
-      <c r="B333" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="334" spans="1:2">
-      <c r="A334" t="s">
-        <v>660</v>
-      </c>
-      <c r="B334" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="335" spans="1:2">
-      <c r="A335" t="s">
-        <v>662</v>
-      </c>
-      <c r="B335" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="336" spans="1:2">
-      <c r="A336" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="B336" s="3" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="337" spans="1:2">
-      <c r="A337" t="s">
-        <v>666</v>
-      </c>
-      <c r="B337" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="338" spans="1:2">
-      <c r="A338" t="s">
-        <v>668</v>
-      </c>
-      <c r="B338" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="339" spans="1:2">
-      <c r="A339" s="3" t="s">
-        <v>670</v>
-      </c>
-      <c r="B339" s="3" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="340" spans="1:2">
-      <c r="A340" s="5" t="s">
-        <v>672</v>
-      </c>
-      <c r="B340" s="5" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="341" spans="1:2">
-      <c r="A341" s="5" t="s">
-        <v>674</v>
-      </c>
-      <c r="B341" s="5" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="342" spans="1:2">
-      <c r="A342" t="s">
-        <v>676</v>
-      </c>
-      <c r="B342" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="343" spans="1:2">
-      <c r="A343" t="s">
-        <v>678</v>
-      </c>
-      <c r="B343" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="344" spans="1:2">
-      <c r="A344" s="3" t="s">
-        <v>680</v>
-      </c>
-      <c r="B344" s="3" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="345" spans="1:2">
-      <c r="A345" t="s">
-        <v>682</v>
-      </c>
-      <c r="B345" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="346" spans="1:2">
-      <c r="A346" t="s">
-        <v>684</v>
-      </c>
-      <c r="B346" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="347" spans="1:2">
-      <c r="A347" t="s">
-        <v>686</v>
-      </c>
-      <c r="B347" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="348" spans="1:2">
-      <c r="A348" s="5" t="s">
-        <v>688</v>
-      </c>
-      <c r="B348" s="5" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="349" spans="1:2">
-      <c r="A349" s="5" t="s">
-        <v>690</v>
-      </c>
-      <c r="B349" s="5" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="350" spans="1:2">
-      <c r="A350" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="B350" s="3" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="351" spans="1:2">
-      <c r="A351" s="3" t="s">
-        <v>694</v>
-      </c>
-      <c r="B351" s="3" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="352" spans="1:2">
-      <c r="A352" t="s">
-        <v>696</v>
-      </c>
-      <c r="B352" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="353" spans="1:2">
-      <c r="A353" s="3" t="s">
-        <v>698</v>
-      </c>
-      <c r="B353" s="3" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="354" spans="1:2">
-      <c r="A354" s="3" t="s">
-        <v>700</v>
-      </c>
-      <c r="B354" s="3" t="s">
-        <v>701</v>
-      </c>
-    </row>
     <row r="355" spans="1:2">
-      <c r="A355" s="5" t="s">
-        <v>702</v>
-      </c>
-      <c r="B355" s="5" t="s">
-        <v>703</v>
-      </c>
+      <c r="A355" s="3"/>
+      <c r="B355" s="3"/>
     </row>
     <row r="356" spans="1:2">
-      <c r="A356" s="3" t="s">
-        <v>704</v>
-      </c>
-      <c r="B356" s="3" t="s">
-        <v>705</v>
-      </c>
+      <c r="A356" s="3"/>
+      <c r="B356" s="3"/>
     </row>
     <row r="357" spans="1:2">
-      <c r="A357" t="s">
-        <v>706</v>
-      </c>
-      <c r="B357" t="s">
-        <v>707</v>
-      </c>
+      <c r="A357"/>
+      <c r="B357"/>
     </row>
     <row r="358" spans="1:2">
-      <c r="A358" s="3" t="s">
-        <v>708</v>
-      </c>
-      <c r="B358" s="3" t="s">
-        <v>709</v>
+      <c r="A358" s="6" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="359" spans="1:2">
       <c r="A359" t="s">
-        <v>710</v>
+        <v>442</v>
       </c>
       <c r="B359" t="s">
-        <v>711</v>
+        <v>443</v>
       </c>
     </row>
     <row r="360" spans="1:2">
       <c r="A360" t="s">
-        <v>712</v>
+        <v>454</v>
       </c>
       <c r="B360" t="s">
-        <v>713</v>
+        <v>455</v>
       </c>
     </row>
     <row r="361" spans="1:2">
-      <c r="A361" s="3" t="s">
-        <v>714</v>
-      </c>
-      <c r="B361" s="3" t="s">
-        <v>715</v>
+      <c r="A361" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="B361" s="5" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="362" spans="1:2">
       <c r="A362" s="3" t="s">
-        <v>716</v>
+        <v>418</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>717</v>
+        <v>419</v>
       </c>
     </row>
     <row r="363" spans="1:2">
-      <c r="A363" t="s">
-        <v>718</v>
-      </c>
-      <c r="B363" t="s">
-        <v>719</v>
+      <c r="A363" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="B363" s="7" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="364" spans="1:2">
       <c r="A364" t="s">
-        <v>720</v>
+        <v>398</v>
       </c>
       <c r="B364" t="s">
-        <v>721</v>
+        <v>399</v>
       </c>
     </row>
     <row r="365" spans="1:2">
-      <c r="A365" s="3" t="s">
-        <v>722</v>
-      </c>
-      <c r="B365" s="3" t="s">
-        <v>723</v>
+      <c r="A365" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B365" s="5" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="366" spans="1:2">
       <c r="A366" s="5" t="s">
-        <v>724</v>
+        <v>189</v>
       </c>
       <c r="B366" s="5" t="s">
-        <v>725</v>
+        <v>190</v>
       </c>
     </row>
     <row r="367" spans="1:2">
-      <c r="A367" t="s">
-        <v>726</v>
-      </c>
-      <c r="B367" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="368" spans="1:2">
-      <c r="A368" t="s">
-        <v>728</v>
-      </c>
-      <c r="B368" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="369" spans="1:2">
-      <c r="A369" t="s">
-        <v>730</v>
-      </c>
-      <c r="B369" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="370" spans="1:2">
-      <c r="A370" s="3" t="s">
-        <v>732</v>
-      </c>
-      <c r="B370" s="3" t="s">
-        <v>733</v>
+      <c r="A367" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B367" s="5" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="371" spans="1:2">
-      <c r="A371" s="3" t="s">
-        <v>734</v>
-      </c>
-      <c r="B371" s="3" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="372" spans="1:2">
-      <c r="A372" t="s">
-        <v>736</v>
-      </c>
-      <c r="B372" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="373" spans="1:2">
-      <c r="A373" t="s">
-        <v>738</v>
-      </c>
-      <c r="B373" t="s">
-        <v>739</v>
-      </c>
+      <c r="A371" s="3"/>
+      <c r="B371" s="3"/>
     </row>
     <row r="374" spans="1:2">
-      <c r="A374" s="3" t="s">
-        <v>740</v>
-      </c>
-      <c r="B374" s="3" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="375" spans="1:2">
-      <c r="A375" s="3" t="s">
-        <v>742</v>
-      </c>
-      <c r="B375" s="3" t="s">
-        <v>743</v>
-      </c>
+      <c r="A374"/>
+      <c r="B374"/>
     </row>
     <row r="376" spans="1:2">
-      <c r="A376" s="3" t="s">
-        <v>744</v>
-      </c>
-      <c r="B376" s="3" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="377" spans="1:2">
-      <c r="A377" t="s">
-        <v>746</v>
-      </c>
-      <c r="B377" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="378" spans="1:2">
-      <c r="A378" t="s">
-        <v>748</v>
-      </c>
-      <c r="B378" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="379" spans="1:2">
-      <c r="A379" s="3" t="s">
-        <v>750</v>
-      </c>
-      <c r="B379" s="3" t="s">
-        <v>751</v>
-      </c>
+      <c r="A376"/>
+      <c r="B376"/>
+    </row>
+    <row r="378" spans="1:2" ht="15.3">
+      <c r="A378" s="1"/>
+      <c r="B378" s="1"/>
     </row>
     <row r="380" spans="1:2">
-      <c r="A380" t="s">
-        <v>752</v>
-      </c>
-      <c r="B380" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="381" spans="1:2">
-      <c r="A381" t="s">
-        <v>754</v>
-      </c>
-      <c r="B381" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="382" spans="1:2">
-      <c r="A382" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="B382" s="3" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="383" spans="1:2">
-      <c r="A383" t="s">
-        <v>758</v>
-      </c>
-      <c r="B383" t="s">
-        <v>759</v>
-      </c>
+      <c r="A380"/>
+      <c r="B380"/>
     </row>
     <row r="384" spans="1:2">
-      <c r="A384" t="s">
-        <v>760</v>
-      </c>
-      <c r="B384" t="s">
-        <v>761</v>
-      </c>
+      <c r="A384" s="3"/>
+      <c r="B384" s="3"/>
     </row>
     <row r="385" spans="1:2">
-      <c r="A385" t="s">
-        <v>762</v>
-      </c>
-      <c r="B385" t="s">
-        <v>763</v>
-      </c>
+      <c r="A385" s="3"/>
+      <c r="B385" s="3"/>
     </row>
     <row r="386" spans="1:2">
-      <c r="A386" s="3"/>
-      <c r="B386" s="3"/>
+      <c r="A386"/>
+      <c r="B386"/>
     </row>
     <row r="387" spans="1:2">
       <c r="A387" s="3"/>
@@ -5945,112 +4713,84 @@
       <c r="B388"/>
     </row>
     <row r="389" spans="1:2">
-      <c r="A389" t="s">
-        <v>764</v>
-      </c>
-      <c r="B389" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="390" spans="1:2">
-      <c r="A390" t="s">
-        <v>269</v>
-      </c>
-      <c r="B390" t="s">
-        <v>270</v>
-      </c>
+      <c r="A389" s="3"/>
+      <c r="B389" s="3"/>
     </row>
     <row r="391" spans="1:2">
-      <c r="A391" s="3" t="s">
-        <v>766</v>
-      </c>
-      <c r="B391" s="3" t="s">
-        <v>767</v>
-      </c>
+      <c r="A391"/>
+      <c r="B391"/>
     </row>
     <row r="392" spans="1:2">
       <c r="A392" s="3"/>
       <c r="B392" s="3"/>
     </row>
     <row r="393" spans="1:2">
-      <c r="A393"/>
-      <c r="B393"/>
+      <c r="A393" s="3"/>
+      <c r="B393" s="3"/>
     </row>
     <row r="394" spans="1:2">
-      <c r="A394" s="3"/>
-      <c r="B394" s="3"/>
+      <c r="A394"/>
+      <c r="B394"/>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395"/>
+      <c r="B395"/>
     </row>
     <row r="396" spans="1:2">
-      <c r="A396"/>
-      <c r="B396"/>
+      <c r="A396" s="3"/>
+      <c r="B396" s="3"/>
     </row>
     <row r="397" spans="1:2">
-      <c r="A397" s="3" t="s">
-        <v>768</v>
-      </c>
-      <c r="B397" s="3" t="s">
-        <v>769</v>
-      </c>
+      <c r="A397"/>
+      <c r="B397"/>
     </row>
     <row r="398" spans="1:2">
-      <c r="A398" s="3"/>
-      <c r="B398" s="3"/>
+      <c r="A398" s="9"/>
+      <c r="B398" s="9"/>
     </row>
     <row r="399" spans="1:2">
-      <c r="A399" s="3" t="s">
-        <v>770</v>
-      </c>
-      <c r="B399" s="3" t="s">
-        <v>771</v>
-      </c>
+      <c r="A399"/>
+      <c r="B399"/>
     </row>
     <row r="400" spans="1:2">
-      <c r="A400" t="s">
-        <v>772</v>
-      </c>
-      <c r="B400" t="s">
-        <v>773</v>
-      </c>
+      <c r="A400"/>
+      <c r="B400"/>
     </row>
     <row r="401" spans="1:2">
       <c r="A401" s="3"/>
       <c r="B401" s="3"/>
     </row>
     <row r="402" spans="1:2">
-      <c r="A402" t="s">
-        <v>774</v>
-      </c>
-      <c r="B402" t="s">
-        <v>775</v>
-      </c>
+      <c r="A402"/>
+      <c r="B402"/>
     </row>
     <row r="403" spans="1:2">
       <c r="A403"/>
       <c r="B403"/>
     </row>
     <row r="404" spans="1:2">
-      <c r="A404" s="3"/>
-      <c r="B404" s="3"/>
+      <c r="A404"/>
+      <c r="B404"/>
     </row>
     <row r="405" spans="1:2">
       <c r="A405"/>
       <c r="B405"/>
     </row>
     <row r="406" spans="1:2">
-      <c r="A406" s="10"/>
-      <c r="B406" s="10"/>
+      <c r="A406" s="3"/>
+      <c r="B406" s="3"/>
     </row>
     <row r="407" spans="1:2">
       <c r="A407"/>
       <c r="B407"/>
     </row>
     <row r="408" spans="1:2">
-      <c r="A408"/>
-      <c r="B408"/>
+      <c r="A408" s="3"/>
+      <c r="B408" s="3"/>
     </row>
     <row r="409" spans="1:2">
-      <c r="A409" s="3"/>
-      <c r="B409" s="3"/>
+      <c r="A409" s="10"/>
+      <c r="B409" s="10"/>
     </row>
     <row r="410" spans="1:2">
       <c r="A410"/>
@@ -6069,32 +4809,24 @@
       <c r="B413"/>
     </row>
     <row r="414" spans="1:2">
-      <c r="A414" s="3"/>
-      <c r="B414" s="3"/>
+      <c r="A414" s="11"/>
+      <c r="B414" s="11"/>
     </row>
     <row r="415" spans="1:2">
-      <c r="A415" t="s">
-        <v>776</v>
-      </c>
-      <c r="B415" t="s">
-        <v>777</v>
-      </c>
+      <c r="A415" s="9"/>
+      <c r="B415" s="9"/>
     </row>
     <row r="416" spans="1:2">
-      <c r="A416" s="3" t="s">
-        <v>778</v>
-      </c>
-      <c r="B416" s="3" t="s">
-        <v>779</v>
-      </c>
+      <c r="A416" s="3"/>
+      <c r="B416" s="3"/>
     </row>
     <row r="417" spans="1:2">
-      <c r="A417" s="11"/>
-      <c r="B417" s="11"/>
+      <c r="A417"/>
+      <c r="B417"/>
     </row>
     <row r="418" spans="1:2">
-      <c r="A418"/>
-      <c r="B418"/>
+      <c r="A418" s="3"/>
+      <c r="B418" s="3"/>
     </row>
     <row r="419" spans="1:2">
       <c r="A419"/>
@@ -6105,58 +4837,17 @@
       <c r="B420"/>
     </row>
     <row r="421" spans="1:2">
-      <c r="A421" t="s">
-        <v>780</v>
-      </c>
-      <c r="B421" t="s">
-        <v>781</v>
-      </c>
+      <c r="A421"/>
+      <c r="B421"/>
     </row>
     <row r="422" spans="1:2">
-      <c r="A422" s="12"/>
-      <c r="B422" s="12"/>
-    </row>
-    <row r="423" spans="1:2">
-      <c r="A423" s="10"/>
-      <c r="B423" s="10"/>
-    </row>
-    <row r="424" spans="1:2">
-      <c r="A424" s="3"/>
-      <c r="B424" s="3"/>
-    </row>
-    <row r="425" spans="1:2">
-      <c r="A425"/>
-      <c r="B425"/>
-    </row>
-    <row r="426" spans="1:2">
-      <c r="A426" s="3"/>
-      <c r="B426" s="3"/>
-    </row>
-    <row r="427" spans="1:2">
-      <c r="A427"/>
-      <c r="B427"/>
-    </row>
-    <row r="428" spans="1:2">
-      <c r="A428" s="3" t="s">
-        <v>782</v>
-      </c>
-      <c r="B428" s="3" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="429" spans="1:2">
-      <c r="A429"/>
-      <c r="B429"/>
-    </row>
-    <row r="430" spans="1:2">
-      <c r="A430"/>
-      <c r="B430"/>
-    </row>
-    <row r="431" spans="1:2">
-      <c r="A431" s="3"/>
-      <c r="B431" s="3"/>
+      <c r="A422" s="3"/>
+      <c r="B422" s="3"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B422">
+    <sortCondition ref="A2:A422"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -6165,11 +4856,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C04419A4-ABD5-463C-A44D-E18099D3F2F0}">
   <dimension ref="A2"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
